--- a/2.RD_CGE/Input_w-t/Projection.xlsx
+++ b/2.RD_CGE/Input_w-t/Projection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20410"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_w-t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E93360-E680-4956-8D12-BA1D84FAB9B5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D83E45F-4E59-4C43-8E27-CBCE41A46DD8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="779" firstSheet="1" activeTab="12" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="779" firstSheet="1" activeTab="10" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseyear" sheetId="12" r:id="rId1"/>
@@ -456,7 +456,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -516,6 +516,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4687,126 +4690,98 @@
       <c r="B6" s="11">
         <v>0</v>
       </c>
-      <c r="C6" s="27">
-        <v>0.01</v>
-      </c>
-      <c r="D6" s="27">
-        <v>0.01</v>
-      </c>
-      <c r="E6" s="27">
-        <v>0.01</v>
-      </c>
-      <c r="F6" s="13">
-        <f t="shared" si="1"/>
-        <v>0.01</v>
-      </c>
-      <c r="G6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="H6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="I6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="L6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="M6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="N6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="O6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="P6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="Q6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="R6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="S6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="T6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="U6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="V6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="W6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="X6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="Y6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="Z6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="AA6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="AB6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="AC6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="AD6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="AE6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="AF6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="AG6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
+      <c r="C6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="D6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="E6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="F6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="G6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="H6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="I6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="J6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="K6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="L6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="M6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="N6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="O6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="P6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="Q6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="R6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="S6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="T6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="U6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="V6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="W6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="X6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="Y6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="Z6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="AA6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="AB6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="AC6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="AD6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="AE6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="AF6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="AG6" s="30">
+        <v>1E-4</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
@@ -6870,7 +6845,7 @@
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H5" s="13">
-        <f t="shared" ref="H5:AE5" si="9">G5+$AI5</f>
+        <f t="shared" ref="H5:AE6" si="9">G5+$AI5</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I5" s="13">
@@ -6966,7 +6941,7 @@
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF5" s="13">
-        <f t="shared" ref="AF5" si="10">AE5+$AI5</f>
+        <f t="shared" ref="AF5:AF6" si="10">AE5+$AI5</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG5" s="13">
@@ -6984,129 +6959,131 @@
       <c r="B6" s="11">
         <v>0</v>
       </c>
-      <c r="C6" s="27">
-        <v>0.01</v>
-      </c>
-      <c r="D6" s="27">
-        <v>0.01</v>
-      </c>
-      <c r="E6" s="27">
-        <v>0.01</v>
-      </c>
-      <c r="F6" s="13">
-        <f t="shared" si="2"/>
-        <v>1.3214285714285715E-2</v>
-      </c>
-      <c r="G6" s="13">
-        <f t="shared" si="3"/>
-        <v>1.6428571428571431E-2</v>
-      </c>
-      <c r="H6" s="13">
-        <f t="shared" ref="H6:AE6" si="11">G6+$AI6</f>
-        <v>1.9642857142857146E-2</v>
-      </c>
-      <c r="I6" s="13">
-        <f t="shared" si="11"/>
-        <v>2.2857142857142861E-2</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="11"/>
-        <v>2.6071428571428575E-2</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="11"/>
-        <v>2.928571428571429E-2</v>
-      </c>
-      <c r="L6" s="13">
-        <f t="shared" si="11"/>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="M6" s="13">
-        <f t="shared" si="11"/>
-        <v>3.5714285714285712E-2</v>
-      </c>
-      <c r="N6" s="13">
-        <f t="shared" si="11"/>
-        <v>3.8928571428571423E-2</v>
-      </c>
-      <c r="O6" s="13">
-        <f t="shared" si="11"/>
-        <v>4.2142857142857135E-2</v>
-      </c>
-      <c r="P6" s="13">
-        <f t="shared" si="11"/>
-        <v>4.5357142857142846E-2</v>
-      </c>
-      <c r="Q6" s="13">
-        <f t="shared" si="11"/>
-        <v>4.8571428571428557E-2</v>
-      </c>
-      <c r="R6" s="13">
-        <f t="shared" si="11"/>
-        <v>5.1785714285714268E-2</v>
-      </c>
-      <c r="S6" s="13">
-        <f t="shared" si="11"/>
-        <v>5.4999999999999979E-2</v>
-      </c>
-      <c r="T6" s="13">
-        <f t="shared" si="11"/>
-        <v>5.8214285714285691E-2</v>
-      </c>
-      <c r="U6" s="13">
-        <f t="shared" si="11"/>
-        <v>6.1428571428571402E-2</v>
-      </c>
-      <c r="V6" s="13">
-        <f t="shared" si="11"/>
-        <v>6.4642857142857113E-2</v>
-      </c>
-      <c r="W6" s="13">
-        <f t="shared" si="11"/>
-        <v>6.7857142857142824E-2</v>
-      </c>
-      <c r="X6" s="13">
-        <f t="shared" si="11"/>
-        <v>7.1071428571428535E-2</v>
-      </c>
-      <c r="Y6" s="13">
-        <f t="shared" si="11"/>
-        <v>7.4285714285714247E-2</v>
-      </c>
-      <c r="Z6" s="13">
-        <f t="shared" si="11"/>
-        <v>7.7499999999999958E-2</v>
-      </c>
-      <c r="AA6" s="13">
-        <f t="shared" si="11"/>
-        <v>8.0714285714285669E-2</v>
-      </c>
-      <c r="AB6" s="13">
-        <f t="shared" si="11"/>
-        <v>8.392857142857138E-2</v>
-      </c>
-      <c r="AC6" s="13">
-        <f t="shared" si="11"/>
-        <v>8.7142857142857091E-2</v>
-      </c>
-      <c r="AD6" s="13">
-        <f t="shared" si="11"/>
-        <v>9.0357142857142803E-2</v>
-      </c>
-      <c r="AE6" s="13">
-        <f t="shared" si="11"/>
-        <v>9.3571428571428514E-2</v>
-      </c>
-      <c r="AF6" s="13">
-        <f t="shared" ref="AF6" si="12">AE6+$AI6</f>
-        <v>9.6785714285714225E-2</v>
-      </c>
-      <c r="AG6" s="13">
-        <v>0.1</v>
+      <c r="C6" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="D6" s="31">
+        <f>C6</f>
+        <v>1E-4</v>
+      </c>
+      <c r="E6" s="31">
+        <f>D6</f>
+        <v>1E-4</v>
+      </c>
+      <c r="F6" s="32">
+        <f t="shared" ref="F6" si="11">E6+$AI6</f>
+        <v>1.3214285714285715E-4</v>
+      </c>
+      <c r="G6" s="32">
+        <f t="shared" ref="G6" si="12">F6+$AI6</f>
+        <v>1.6428571428571431E-4</v>
+      </c>
+      <c r="H6" s="32">
+        <f t="shared" si="9"/>
+        <v>1.9642857142857146E-4</v>
+      </c>
+      <c r="I6" s="32">
+        <f t="shared" si="9"/>
+        <v>2.2857142857142862E-4</v>
+      </c>
+      <c r="J6" s="32">
+        <f t="shared" si="9"/>
+        <v>2.6071428571428578E-4</v>
+      </c>
+      <c r="K6" s="32">
+        <f t="shared" si="9"/>
+        <v>2.9285714285714294E-4</v>
+      </c>
+      <c r="L6" s="32">
+        <f t="shared" si="9"/>
+        <v>3.2500000000000009E-4</v>
+      </c>
+      <c r="M6" s="32">
+        <f t="shared" si="9"/>
+        <v>3.5714285714285725E-4</v>
+      </c>
+      <c r="N6" s="32">
+        <f t="shared" si="9"/>
+        <v>3.8928571428571441E-4</v>
+      </c>
+      <c r="O6" s="32">
+        <f t="shared" si="9"/>
+        <v>4.2142857142857157E-4</v>
+      </c>
+      <c r="P6" s="32">
+        <f t="shared" si="9"/>
+        <v>4.5357142857142872E-4</v>
+      </c>
+      <c r="Q6" s="32">
+        <f t="shared" si="9"/>
+        <v>4.8571428571428588E-4</v>
+      </c>
+      <c r="R6" s="32">
+        <f t="shared" si="9"/>
+        <v>5.1785714285714304E-4</v>
+      </c>
+      <c r="S6" s="32">
+        <f t="shared" si="9"/>
+        <v>5.5000000000000014E-4</v>
+      </c>
+      <c r="T6" s="32">
+        <f t="shared" si="9"/>
+        <v>5.8214285714285724E-4</v>
+      </c>
+      <c r="U6" s="32">
+        <f t="shared" si="9"/>
+        <v>6.1428571428571435E-4</v>
+      </c>
+      <c r="V6" s="32">
+        <f t="shared" si="9"/>
+        <v>6.4642857142857145E-4</v>
+      </c>
+      <c r="W6" s="32">
+        <f t="shared" si="9"/>
+        <v>6.7857142857142855E-4</v>
+      </c>
+      <c r="X6" s="32">
+        <f t="shared" si="9"/>
+        <v>7.1071428571428566E-4</v>
+      </c>
+      <c r="Y6" s="32">
+        <f t="shared" si="9"/>
+        <v>7.4285714285714276E-4</v>
+      </c>
+      <c r="Z6" s="32">
+        <f t="shared" si="9"/>
+        <v>7.7499999999999986E-4</v>
+      </c>
+      <c r="AA6" s="32">
+        <f t="shared" si="9"/>
+        <v>8.0714285714285697E-4</v>
+      </c>
+      <c r="AB6" s="32">
+        <f t="shared" si="9"/>
+        <v>8.3928571428571407E-4</v>
+      </c>
+      <c r="AC6" s="32">
+        <f t="shared" si="9"/>
+        <v>8.7142857142857117E-4</v>
+      </c>
+      <c r="AD6" s="32">
+        <f t="shared" si="9"/>
+        <v>9.0357142857142828E-4</v>
+      </c>
+      <c r="AE6" s="32">
+        <f t="shared" si="9"/>
+        <v>9.3571428571428538E-4</v>
+      </c>
+      <c r="AF6" s="32">
+        <f t="shared" si="10"/>
+        <v>9.6785714285714248E-4</v>
+      </c>
+      <c r="AG6" s="32">
+        <v>1E-3</v>
       </c>
       <c r="AI6" s="28">
         <f t="shared" si="6"/>
-        <v>3.2142857142857147E-3</v>
+        <v>3.2142857142857144E-5</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
@@ -9340,135 +9317,135 @@
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="35">
         <v>0</v>
       </c>
-      <c r="C6" s="27">
-        <v>0.01</v>
-      </c>
-      <c r="D6" s="27">
-        <v>0.01</v>
-      </c>
-      <c r="E6" s="27">
-        <v>0.01</v>
-      </c>
-      <c r="F6" s="13">
-        <f t="shared" si="1"/>
-        <v>2.7499999999999997E-2</v>
-      </c>
-      <c r="G6" s="13">
-        <f t="shared" si="1"/>
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="H6" s="13">
-        <f t="shared" si="0"/>
-        <v>6.25E-2</v>
-      </c>
-      <c r="I6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.08</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="0"/>
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.115</v>
-      </c>
-      <c r="L6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="M6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.15</v>
-      </c>
-      <c r="N6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.16749999999999998</v>
-      </c>
-      <c r="O6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.18499999999999997</v>
-      </c>
-      <c r="P6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.20249999999999996</v>
-      </c>
-      <c r="Q6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.21999999999999995</v>
-      </c>
-      <c r="R6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.23749999999999993</v>
-      </c>
-      <c r="S6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.25499999999999995</v>
-      </c>
-      <c r="T6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.27249999999999996</v>
-      </c>
-      <c r="U6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="V6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.3075</v>
-      </c>
-      <c r="W6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="X6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.34250000000000003</v>
-      </c>
-      <c r="Y6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="Z6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.37750000000000006</v>
-      </c>
-      <c r="AA6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.39500000000000007</v>
-      </c>
-      <c r="AB6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.41250000000000009</v>
-      </c>
-      <c r="AC6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.4300000000000001</v>
-      </c>
-      <c r="AD6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.44750000000000012</v>
-      </c>
-      <c r="AE6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.46500000000000014</v>
-      </c>
-      <c r="AF6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.48250000000000015</v>
-      </c>
-      <c r="AG6" s="13">
-        <v>0.5</v>
+      <c r="C6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="D6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="E6" s="30">
+        <v>1E-4</v>
+      </c>
+      <c r="F6" s="32">
+        <f t="shared" ref="F6" si="3">E6+$AI6</f>
+        <v>1.8821428571428572E-3</v>
+      </c>
+      <c r="G6" s="32">
+        <f t="shared" ref="G6:AF6" si="4">F6+$AI6</f>
+        <v>3.6642857142857145E-3</v>
+      </c>
+      <c r="H6" s="32">
+        <f t="shared" si="4"/>
+        <v>5.4464285714285717E-3</v>
+      </c>
+      <c r="I6" s="32">
+        <f t="shared" si="4"/>
+        <v>7.2285714285714288E-3</v>
+      </c>
+      <c r="J6" s="32">
+        <f t="shared" si="4"/>
+        <v>9.0107142857142851E-3</v>
+      </c>
+      <c r="K6" s="32">
+        <f t="shared" si="4"/>
+        <v>1.0792857142857142E-2</v>
+      </c>
+      <c r="L6" s="32">
+        <f t="shared" si="4"/>
+        <v>1.2574999999999999E-2</v>
+      </c>
+      <c r="M6" s="32">
+        <f t="shared" si="4"/>
+        <v>1.4357142857142857E-2</v>
+      </c>
+      <c r="N6" s="32">
+        <f t="shared" si="4"/>
+        <v>1.6139285714285714E-2</v>
+      </c>
+      <c r="O6" s="32">
+        <f t="shared" si="4"/>
+        <v>1.7921428571428571E-2</v>
+      </c>
+      <c r="P6" s="32">
+        <f t="shared" si="4"/>
+        <v>1.9703571428571428E-2</v>
+      </c>
+      <c r="Q6" s="32">
+        <f t="shared" si="4"/>
+        <v>2.1485714285714285E-2</v>
+      </c>
+      <c r="R6" s="32">
+        <f t="shared" si="4"/>
+        <v>2.3267857142857142E-2</v>
+      </c>
+      <c r="S6" s="32">
+        <f t="shared" si="4"/>
+        <v>2.5049999999999999E-2</v>
+      </c>
+      <c r="T6" s="32">
+        <f t="shared" si="4"/>
+        <v>2.6832142857142856E-2</v>
+      </c>
+      <c r="U6" s="32">
+        <f t="shared" si="4"/>
+        <v>2.8614285714285714E-2</v>
+      </c>
+      <c r="V6" s="32">
+        <f t="shared" si="4"/>
+        <v>3.0396428571428571E-2</v>
+      </c>
+      <c r="W6" s="32">
+        <f t="shared" si="4"/>
+        <v>3.2178571428571431E-2</v>
+      </c>
+      <c r="X6" s="32">
+        <f t="shared" si="4"/>
+        <v>3.3960714285714289E-2</v>
+      </c>
+      <c r="Y6" s="32">
+        <f t="shared" si="4"/>
+        <v>3.5742857142857146E-2</v>
+      </c>
+      <c r="Z6" s="32">
+        <f t="shared" si="4"/>
+        <v>3.7525000000000003E-2</v>
+      </c>
+      <c r="AA6" s="32">
+        <f t="shared" si="4"/>
+        <v>3.930714285714286E-2</v>
+      </c>
+      <c r="AB6" s="32">
+        <f t="shared" si="4"/>
+        <v>4.1089285714285717E-2</v>
+      </c>
+      <c r="AC6" s="32">
+        <f t="shared" si="4"/>
+        <v>4.2871428571428574E-2</v>
+      </c>
+      <c r="AD6" s="32">
+        <f t="shared" si="4"/>
+        <v>4.4653571428571431E-2</v>
+      </c>
+      <c r="AE6" s="32">
+        <f t="shared" si="4"/>
+        <v>4.6435714285714288E-2</v>
+      </c>
+      <c r="AF6" s="32">
+        <f t="shared" si="4"/>
+        <v>4.8217857142857146E-2</v>
+      </c>
+      <c r="AG6" s="32">
+        <v>0.05</v>
       </c>
       <c r="AI6" s="28">
         <f t="shared" si="2"/>
-        <v>1.7499999999999998E-2</v>
+        <v>1.7821428571428571E-3</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
@@ -10176,83 +10153,83 @@
         <v>0.13250000000000001</v>
       </c>
       <c r="M12" s="13">
-        <f t="shared" ref="M12:AF18" si="3">L12+$AI12</f>
+        <f t="shared" ref="M12:AF18" si="5">L12+$AI12</f>
         <v>0.15</v>
       </c>
       <c r="N12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.16749999999999998</v>
       </c>
       <c r="O12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.18499999999999997</v>
       </c>
       <c r="P12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.20249999999999996</v>
       </c>
       <c r="Q12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.21999999999999995</v>
       </c>
       <c r="R12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.23749999999999993</v>
       </c>
       <c r="S12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.25499999999999995</v>
       </c>
       <c r="T12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.27249999999999996</v>
       </c>
       <c r="U12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="V12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3075</v>
       </c>
       <c r="W12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG12" s="13">
@@ -10344,47 +10321,47 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="V13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3075</v>
       </c>
       <c r="W13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG13" s="13">
@@ -10476,47 +10453,47 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="V14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3075</v>
       </c>
       <c r="W14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG14" s="13">
@@ -10608,47 +10585,47 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="V15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3075</v>
       </c>
       <c r="W15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG15" s="13">
@@ -10740,47 +10717,47 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="V16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3075</v>
       </c>
       <c r="W16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG16" s="13">
@@ -10872,47 +10849,47 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="V17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.3075</v>
       </c>
       <c r="W17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG17" s="13">
@@ -11004,47 +10981,47 @@
         <v>1.1857142857142855</v>
       </c>
       <c r="V18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.2535714285714283</v>
       </c>
       <c r="W18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.3214285714285712</v>
       </c>
       <c r="X18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.389285714285714</v>
       </c>
       <c r="Y18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.4571428571428569</v>
       </c>
       <c r="Z18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.5249999999999997</v>
       </c>
       <c r="AA18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.5928571428571425</v>
       </c>
       <c r="AB18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.6607142857142854</v>
       </c>
       <c r="AC18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.7285714285714282</v>
       </c>
       <c r="AD18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.796428571428571</v>
       </c>
       <c r="AE18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.8642857142857139</v>
       </c>
       <c r="AF18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.9321428571428567</v>
       </c>
       <c r="AG18" s="13">

--- a/2.RD_CGE/Input_w-t/Projection.xlsx
+++ b/2.RD_CGE/Input_w-t/Projection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20412"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_w-t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D83E45F-4E59-4C43-8E27-CBCE41A46DD8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1D908C-F777-4C5D-8558-5DBAD3F6C8FD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="779" firstSheet="1" activeTab="10" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="870" activeTab="9" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseyear" sheetId="12" r:id="rId1"/>
@@ -2450,97 +2450,97 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="D3">
-        <v>0.99960000000000004</v>
+        <v>0.9506</v>
       </c>
       <c r="E3">
-        <v>0.97960800000000003</v>
+        <v>0.93158799999999997</v>
       </c>
       <c r="F3">
-        <v>0.96001584000000006</v>
+        <v>0.91295623999999997</v>
       </c>
       <c r="G3">
-        <v>0.94081552320000006</v>
+        <v>0.89469711519999995</v>
       </c>
       <c r="H3">
-        <v>0.92199921273600005</v>
+        <v>0.87680317289599996</v>
       </c>
       <c r="I3">
-        <v>0.90355922848128001</v>
+        <v>0.85926710943807993</v>
       </c>
       <c r="J3">
-        <v>0.88548804391165437</v>
+        <v>0.84208176724931838</v>
       </c>
       <c r="K3">
-        <v>0.8677782830334213</v>
+        <v>0.82524013190433199</v>
       </c>
       <c r="L3">
-        <v>0.85042271737275288</v>
+        <v>0.80873532926624536</v>
       </c>
       <c r="M3">
-        <v>0.83341426302529786</v>
+        <v>0.79256062268092042</v>
       </c>
       <c r="N3">
-        <v>0.81674597776479185</v>
+        <v>0.776709410227302</v>
       </c>
       <c r="O3">
-        <v>0.80041105820949598</v>
+        <v>0.761175222022756</v>
       </c>
       <c r="P3">
-        <v>0.78440283704530611</v>
+        <v>0.74595171758230083</v>
       </c>
       <c r="Q3">
-        <v>0.76871478030439999</v>
+        <v>0.73103268323065485</v>
       </c>
       <c r="R3">
-        <v>0.75334048469831194</v>
+        <v>0.71641202956604177</v>
       </c>
       <c r="S3">
-        <v>0.73827367500434571</v>
+        <v>0.7020837889747209</v>
       </c>
       <c r="T3">
-        <v>0.72350820150425876</v>
+        <v>0.68804211319522646</v>
       </c>
       <c r="U3">
-        <v>0.7090380374741736</v>
+        <v>0.67428127093132195</v>
       </c>
       <c r="V3">
-        <v>0.69485727672469011</v>
+        <v>0.66079564551269554</v>
       </c>
       <c r="W3">
-        <v>0.68096013119019627</v>
+        <v>0.64757973260244162</v>
       </c>
       <c r="X3">
-        <v>0.66734092856639238</v>
+        <v>0.63462813795039275</v>
       </c>
       <c r="Y3">
-        <v>0.65399410999506458</v>
+        <v>0.62193557519138487</v>
       </c>
       <c r="Z3">
-        <v>0.64091422779516327</v>
+        <v>0.60949686368755718</v>
       </c>
       <c r="AA3">
-        <v>0.62809594323925999</v>
+        <v>0.59730692641380601</v>
       </c>
       <c r="AB3">
-        <v>0.6155340243744748</v>
+        <v>0.58536078788552992</v>
       </c>
       <c r="AC3">
-        <v>0.60322334388698529</v>
+        <v>0.57365357212781931</v>
       </c>
       <c r="AD3">
-        <v>0.59115887700924563</v>
+        <v>0.56218050068526293</v>
       </c>
       <c r="AE3">
-        <v>0.57933569946906072</v>
+        <v>0.55093689067155771</v>
       </c>
       <c r="AF3">
-        <v>0.56774898547967956</v>
+        <v>0.53991815285812661</v>
       </c>
       <c r="AG3">
-        <v>0.55639400577008602</v>
+        <v>0.52911978980096408</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
@@ -2554,94 +2554,94 @@
         <v>0.97</v>
       </c>
       <c r="D4">
-        <v>0.94574999999999998</v>
+        <v>0.9506</v>
       </c>
       <c r="E4">
-        <v>0.92210625000000002</v>
+        <v>0.93158799999999997</v>
       </c>
       <c r="F4">
-        <v>0.89905359375000005</v>
+        <v>0.91295623999999997</v>
       </c>
       <c r="G4">
-        <v>0.87657725390625008</v>
+        <v>0.89469711519999995</v>
       </c>
       <c r="H4">
-        <v>0.85466282255859383</v>
+        <v>0.87680317289599996</v>
       </c>
       <c r="I4">
-        <v>0.83329625199462898</v>
+        <v>0.85926710943807993</v>
       </c>
       <c r="J4">
-        <v>0.81246384569476326</v>
+        <v>0.84208176724931838</v>
       </c>
       <c r="K4">
-        <v>0.79215224955239416</v>
+        <v>0.82524013190433199</v>
       </c>
       <c r="L4">
-        <v>0.77234844331358432</v>
+        <v>0.80873532926624536</v>
       </c>
       <c r="M4">
-        <v>0.75303973223074472</v>
+        <v>0.79256062268092042</v>
       </c>
       <c r="N4">
-        <v>0.7342137389249761</v>
+        <v>0.776709410227302</v>
       </c>
       <c r="O4">
-        <v>0.7158583954518517</v>
+        <v>0.761175222022756</v>
       </c>
       <c r="P4">
-        <v>0.69796193556555541</v>
+        <v>0.74595171758230083</v>
       </c>
       <c r="Q4">
-        <v>0.68051288717641656</v>
+        <v>0.73103268323065485</v>
       </c>
       <c r="R4">
-        <v>0.6635000649970062</v>
+        <v>0.71641202956604177</v>
       </c>
       <c r="S4">
-        <v>0.64691256337208103</v>
+        <v>0.7020837889747209</v>
       </c>
       <c r="T4">
-        <v>0.63073974928777898</v>
+        <v>0.68804211319522646</v>
       </c>
       <c r="U4">
-        <v>0.61497125555558452</v>
+        <v>0.67428127093132195</v>
       </c>
       <c r="V4">
-        <v>0.59959697416669488</v>
+        <v>0.66079564551269554</v>
       </c>
       <c r="W4">
-        <v>0.58460704981252753</v>
+        <v>0.64757973260244162</v>
       </c>
       <c r="X4">
-        <v>0.56999187356721437</v>
+        <v>0.63462813795039275</v>
       </c>
       <c r="Y4">
-        <v>0.555742076728034</v>
+        <v>0.62193557519138487</v>
       </c>
       <c r="Z4">
-        <v>0.54184852480983314</v>
+        <v>0.60949686368755718</v>
       </c>
       <c r="AA4">
-        <v>0.5283023116895873</v>
+        <v>0.59730692641380601</v>
       </c>
       <c r="AB4">
-        <v>0.5150947538973476</v>
+        <v>0.58536078788552992</v>
       </c>
       <c r="AC4">
-        <v>0.50221738504991387</v>
+        <v>0.57365357212781931</v>
       </c>
       <c r="AD4">
-        <v>0.489661950423666</v>
+        <v>0.56218050068526293</v>
       </c>
       <c r="AE4">
-        <v>0.47742040166307437</v>
+        <v>0.55093689067155771</v>
       </c>
       <c r="AF4">
-        <v>0.46548489162149753</v>
+        <v>0.53991815285812661</v>
       </c>
       <c r="AG4">
-        <v>0.4538477693309601</v>
+        <v>0.52911978980096408</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
@@ -2655,94 +2655,94 @@
         <v>0.97</v>
       </c>
       <c r="D5">
-        <v>0.96514999999999995</v>
+        <v>0.9506</v>
       </c>
       <c r="E5">
-        <v>0.96032424999999999</v>
+        <v>0.93158799999999997</v>
       </c>
       <c r="F5">
-        <v>0.95552262874999994</v>
+        <v>0.91295623999999997</v>
       </c>
       <c r="G5">
-        <v>0.95074501560624991</v>
+        <v>0.89469711519999995</v>
       </c>
       <c r="H5">
-        <v>0.94599129052821862</v>
+        <v>0.87680317289599996</v>
       </c>
       <c r="I5">
-        <v>0.94126133407557755</v>
+        <v>0.85926710943807993</v>
       </c>
       <c r="J5">
-        <v>0.93655502740519969</v>
+        <v>0.84208176724931838</v>
       </c>
       <c r="K5">
-        <v>0.93187225226817372</v>
+        <v>0.82524013190433199</v>
       </c>
       <c r="L5">
-        <v>0.9272128910068328</v>
+        <v>0.80873532926624536</v>
       </c>
       <c r="M5">
-        <v>0.92257682655179862</v>
+        <v>0.79256062268092042</v>
       </c>
       <c r="N5">
-        <v>0.91796394241903967</v>
+        <v>0.776709410227302</v>
       </c>
       <c r="O5">
-        <v>0.91337412270694451</v>
+        <v>0.761175222022756</v>
       </c>
       <c r="P5">
-        <v>0.90880725209340985</v>
+        <v>0.74595171758230083</v>
       </c>
       <c r="Q5">
-        <v>0.90426321583294278</v>
+        <v>0.73103268323065485</v>
       </c>
       <c r="R5">
-        <v>0.89974189975377805</v>
+        <v>0.71641202956604177</v>
       </c>
       <c r="S5">
-        <v>0.8952431902550092</v>
+        <v>0.7020837889747209</v>
       </c>
       <c r="T5">
-        <v>0.89076697430373419</v>
+        <v>0.68804211319522646</v>
       </c>
       <c r="U5">
-        <v>0.88631313943221557</v>
+        <v>0.67428127093132195</v>
       </c>
       <c r="V5">
-        <v>0.88188157373505449</v>
+        <v>0.66079564551269554</v>
       </c>
       <c r="W5">
-        <v>0.87747216586637922</v>
+        <v>0.64757973260244162</v>
       </c>
       <c r="X5">
-        <v>0.87308480503704733</v>
+        <v>0.63462813795039275</v>
       </c>
       <c r="Y5">
-        <v>0.86871938101186208</v>
+        <v>0.62193557519138487</v>
       </c>
       <c r="Z5">
-        <v>0.86437578410680271</v>
+        <v>0.60949686368755718</v>
       </c>
       <c r="AA5">
-        <v>0.86005390518626867</v>
+        <v>0.59730692641380601</v>
       </c>
       <c r="AB5">
-        <v>0.85575363566033735</v>
+        <v>0.58536078788552992</v>
       </c>
       <c r="AC5">
-        <v>0.85147486748203571</v>
+        <v>0.57365357212781931</v>
       </c>
       <c r="AD5">
-        <v>0.84721749314462558</v>
+        <v>0.56218050068526293</v>
       </c>
       <c r="AE5">
-        <v>0.84298140567890245</v>
+        <v>0.55093689067155771</v>
       </c>
       <c r="AF5">
-        <v>0.8387664986505079</v>
+        <v>0.53991815285812661</v>
       </c>
       <c r="AG5">
-        <v>0.83457266615725534</v>
+        <v>0.52911978980096408</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
@@ -2756,94 +2756,94 @@
         <v>0.97</v>
       </c>
       <c r="D6">
-        <v>0.96514999999999995</v>
+        <v>0.9506</v>
       </c>
       <c r="E6">
-        <v>0.96032424999999999</v>
+        <v>0.93158799999999997</v>
       </c>
       <c r="F6">
-        <v>0.95552262874999994</v>
+        <v>0.91295623999999997</v>
       </c>
       <c r="G6">
-        <v>0.95074501560624991</v>
+        <v>0.89469711519999995</v>
       </c>
       <c r="H6">
-        <v>0.94599129052821862</v>
+        <v>0.87680317289599996</v>
       </c>
       <c r="I6">
-        <v>0.94126133407557755</v>
+        <v>0.85926710943807993</v>
       </c>
       <c r="J6">
-        <v>0.93655502740519969</v>
+        <v>0.84208176724931838</v>
       </c>
       <c r="K6">
-        <v>0.93187225226817372</v>
+        <v>0.82524013190433199</v>
       </c>
       <c r="L6">
-        <v>0.9272128910068328</v>
+        <v>0.80873532926624536</v>
       </c>
       <c r="M6">
-        <v>0.92257682655179862</v>
+        <v>0.79256062268092042</v>
       </c>
       <c r="N6">
-        <v>0.91796394241903967</v>
+        <v>0.776709410227302</v>
       </c>
       <c r="O6">
-        <v>0.91337412270694451</v>
+        <v>0.761175222022756</v>
       </c>
       <c r="P6">
-        <v>0.90880725209340985</v>
+        <v>0.74595171758230083</v>
       </c>
       <c r="Q6">
-        <v>0.90426321583294278</v>
+        <v>0.73103268323065485</v>
       </c>
       <c r="R6">
-        <v>0.89974189975377805</v>
+        <v>0.71641202956604177</v>
       </c>
       <c r="S6">
-        <v>0.8952431902550092</v>
+        <v>0.7020837889747209</v>
       </c>
       <c r="T6">
-        <v>0.89076697430373419</v>
+        <v>0.68804211319522646</v>
       </c>
       <c r="U6">
-        <v>0.88631313943221557</v>
+        <v>0.67428127093132195</v>
       </c>
       <c r="V6">
-        <v>0.88188157373505449</v>
+        <v>0.66079564551269554</v>
       </c>
       <c r="W6">
-        <v>0.87747216586637922</v>
+        <v>0.64757973260244162</v>
       </c>
       <c r="X6">
-        <v>0.87308480503704733</v>
+        <v>0.63462813795039275</v>
       </c>
       <c r="Y6">
-        <v>0.86871938101186208</v>
+        <v>0.62193557519138487</v>
       </c>
       <c r="Z6">
-        <v>0.86437578410680271</v>
+        <v>0.60949686368755718</v>
       </c>
       <c r="AA6">
-        <v>0.86005390518626867</v>
+        <v>0.59730692641380601</v>
       </c>
       <c r="AB6">
-        <v>0.85575363566033735</v>
+        <v>0.58536078788552992</v>
       </c>
       <c r="AC6">
-        <v>0.85147486748203571</v>
+        <v>0.57365357212781931</v>
       </c>
       <c r="AD6">
-        <v>0.84721749314462558</v>
+        <v>0.56218050068526293</v>
       </c>
       <c r="AE6">
-        <v>0.84298140567890245</v>
+        <v>0.55093689067155771</v>
       </c>
       <c r="AF6">
-        <v>0.8387664986505079</v>
+        <v>0.53991815285812661</v>
       </c>
       <c r="AG6">
-        <v>0.83457266615725534</v>
+        <v>0.52911978980096408</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
@@ -2857,94 +2857,94 @@
         <v>0.97</v>
       </c>
       <c r="D7">
-        <v>0.96514999999999995</v>
+        <v>0.9506</v>
       </c>
       <c r="E7">
-        <v>0.96032424999999999</v>
+        <v>0.93158799999999997</v>
       </c>
       <c r="F7">
-        <v>0.95552262874999994</v>
+        <v>0.91295623999999997</v>
       </c>
       <c r="G7">
-        <v>0.95074501560624991</v>
+        <v>0.89469711519999995</v>
       </c>
       <c r="H7">
-        <v>0.94599129052821862</v>
+        <v>0.87680317289599996</v>
       </c>
       <c r="I7">
-        <v>0.94126133407557755</v>
+        <v>0.85926710943807993</v>
       </c>
       <c r="J7">
-        <v>0.93655502740519969</v>
+        <v>0.84208176724931838</v>
       </c>
       <c r="K7">
-        <v>0.93187225226817372</v>
+        <v>0.82524013190433199</v>
       </c>
       <c r="L7">
-        <v>0.9272128910068328</v>
+        <v>0.80873532926624536</v>
       </c>
       <c r="M7">
-        <v>0.92257682655179862</v>
+        <v>0.79256062268092042</v>
       </c>
       <c r="N7">
-        <v>0.91796394241903967</v>
+        <v>0.776709410227302</v>
       </c>
       <c r="O7">
-        <v>0.91337412270694451</v>
+        <v>0.761175222022756</v>
       </c>
       <c r="P7">
-        <v>0.90880725209340985</v>
+        <v>0.74595171758230083</v>
       </c>
       <c r="Q7">
-        <v>0.90426321583294278</v>
+        <v>0.73103268323065485</v>
       </c>
       <c r="R7">
-        <v>0.89974189975377805</v>
+        <v>0.71641202956604177</v>
       </c>
       <c r="S7">
-        <v>0.8952431902550092</v>
+        <v>0.7020837889747209</v>
       </c>
       <c r="T7">
-        <v>0.89076697430373419</v>
+        <v>0.68804211319522646</v>
       </c>
       <c r="U7">
-        <v>0.88631313943221557</v>
+        <v>0.67428127093132195</v>
       </c>
       <c r="V7">
-        <v>0.88188157373505449</v>
+        <v>0.66079564551269554</v>
       </c>
       <c r="W7">
-        <v>0.87747216586637922</v>
+        <v>0.64757973260244162</v>
       </c>
       <c r="X7">
-        <v>0.87308480503704733</v>
+        <v>0.63462813795039275</v>
       </c>
       <c r="Y7">
-        <v>0.86871938101186208</v>
+        <v>0.62193557519138487</v>
       </c>
       <c r="Z7">
-        <v>0.86437578410680271</v>
+        <v>0.60949686368755718</v>
       </c>
       <c r="AA7">
-        <v>0.86005390518626867</v>
+        <v>0.59730692641380601</v>
       </c>
       <c r="AB7">
-        <v>0.85575363566033735</v>
+        <v>0.58536078788552992</v>
       </c>
       <c r="AC7">
-        <v>0.85147486748203571</v>
+        <v>0.57365357212781931</v>
       </c>
       <c r="AD7">
-        <v>0.84721749314462558</v>
+        <v>0.56218050068526293</v>
       </c>
       <c r="AE7">
-        <v>0.84298140567890245</v>
+        <v>0.55093689067155771</v>
       </c>
       <c r="AF7">
-        <v>0.8387664986505079</v>
+        <v>0.53991815285812661</v>
       </c>
       <c r="AG7">
-        <v>0.83457266615725534</v>
+        <v>0.52911978980096408</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -3059,94 +3059,94 @@
         <v>0.97</v>
       </c>
       <c r="D9">
-        <v>0.96029999999999993</v>
+        <v>0.9506</v>
       </c>
       <c r="E9">
-        <v>0.9506969999999999</v>
+        <v>0.93158799999999997</v>
       </c>
       <c r="F9">
-        <v>0.9411900299999999</v>
+        <v>0.91295623999999997</v>
       </c>
       <c r="G9">
-        <v>0.93177812969999985</v>
+        <v>0.89469711519999995</v>
       </c>
       <c r="H9">
-        <v>0.92246034840299984</v>
+        <v>0.87680317289599996</v>
       </c>
       <c r="I9">
-        <v>0.91323574491896986</v>
+        <v>0.85926710943807993</v>
       </c>
       <c r="J9">
-        <v>0.90410338746978014</v>
+        <v>0.84208176724931838</v>
       </c>
       <c r="K9">
-        <v>0.89506235359508235</v>
+        <v>0.82524013190433199</v>
       </c>
       <c r="L9">
-        <v>0.88611173005913157</v>
+        <v>0.80873532926624536</v>
       </c>
       <c r="M9">
-        <v>0.87725061275854022</v>
+        <v>0.79256062268092042</v>
       </c>
       <c r="N9">
-        <v>0.86847810663095482</v>
+        <v>0.776709410227302</v>
       </c>
       <c r="O9">
-        <v>0.85979332556464527</v>
+        <v>0.761175222022756</v>
       </c>
       <c r="P9">
-        <v>0.85119539230899877</v>
+        <v>0.74595171758230083</v>
       </c>
       <c r="Q9">
-        <v>0.84268343838590876</v>
+        <v>0.73103268323065485</v>
       </c>
       <c r="R9">
-        <v>0.83425660400204971</v>
+        <v>0.71641202956604177</v>
       </c>
       <c r="S9">
-        <v>0.82591403796202922</v>
+        <v>0.7020837889747209</v>
       </c>
       <c r="T9">
-        <v>0.81765489758240895</v>
+        <v>0.68804211319522646</v>
       </c>
       <c r="U9">
-        <v>0.80947834860658485</v>
+        <v>0.67428127093132195</v>
       </c>
       <c r="V9">
-        <v>0.801383565120519</v>
+        <v>0.66079564551269554</v>
       </c>
       <c r="W9">
-        <v>0.79336972946931383</v>
+        <v>0.64757973260244162</v>
       </c>
       <c r="X9">
-        <v>0.78543603217462066</v>
+        <v>0.63462813795039275</v>
       </c>
       <c r="Y9">
-        <v>0.77758167185287441</v>
+        <v>0.62193557519138487</v>
       </c>
       <c r="Z9">
-        <v>0.76980585513434563</v>
+        <v>0.60949686368755718</v>
       </c>
       <c r="AA9">
-        <v>0.76210779658300221</v>
+        <v>0.59730692641380601</v>
       </c>
       <c r="AB9">
-        <v>0.7544867186171722</v>
+        <v>0.58536078788552992</v>
       </c>
       <c r="AC9">
-        <v>0.74694185143100045</v>
+        <v>0.57365357212781931</v>
       </c>
       <c r="AD9">
-        <v>0.7394724329166904</v>
+        <v>0.56218050068526293</v>
       </c>
       <c r="AE9">
-        <v>0.73207770858752352</v>
+        <v>0.55093689067155771</v>
       </c>
       <c r="AF9">
-        <v>0.72475693150164833</v>
+        <v>0.53991815285812661</v>
       </c>
       <c r="AG9">
-        <v>0.71750936218663186</v>
+        <v>0.52911978980096408</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -3160,94 +3160,94 @@
         <v>0.97</v>
       </c>
       <c r="D10">
-        <v>0.94089999999999996</v>
+        <v>0.9506</v>
       </c>
       <c r="E10">
-        <v>0.91737749999999996</v>
+        <v>0.93158799999999997</v>
       </c>
       <c r="F10">
-        <v>0.89444306249999994</v>
+        <v>0.91295623999999997</v>
       </c>
       <c r="G10">
-        <v>0.87208198593749997</v>
+        <v>0.89469711519999995</v>
       </c>
       <c r="H10">
-        <v>0.85027993628906251</v>
+        <v>0.87680317289599996</v>
       </c>
       <c r="I10">
-        <v>0.8290229378818359</v>
+        <v>0.85926710943807993</v>
       </c>
       <c r="J10">
-        <v>0.80829736443478994</v>
+        <v>0.84208176724931838</v>
       </c>
       <c r="K10">
-        <v>0.78808993032392016</v>
+        <v>0.82524013190433199</v>
       </c>
       <c r="L10">
-        <v>0.7683876820658222</v>
+        <v>0.80873532926624536</v>
       </c>
       <c r="M10">
-        <v>0.74917799001417662</v>
+        <v>0.79256062268092042</v>
       </c>
       <c r="N10">
-        <v>0.72670265031375136</v>
+        <v>0.776709410227302</v>
       </c>
       <c r="O10">
-        <v>0.7049015708043388</v>
+        <v>0.761175222022756</v>
       </c>
       <c r="P10">
-        <v>0.68375452368020861</v>
+        <v>0.74595171758230083</v>
       </c>
       <c r="Q10">
-        <v>0.66324188796980232</v>
+        <v>0.73103268323065485</v>
       </c>
       <c r="R10">
-        <v>0.64334463133070829</v>
+        <v>0.71641202956604177</v>
       </c>
       <c r="S10">
-        <v>0.62404429239078707</v>
+        <v>0.7020837889747209</v>
       </c>
       <c r="T10">
-        <v>0.60532296361906346</v>
+        <v>0.68804211319522646</v>
       </c>
       <c r="U10">
-        <v>0.58716327471049157</v>
+        <v>0.67428127093132195</v>
       </c>
       <c r="V10">
-        <v>0.56954837646917678</v>
+        <v>0.66079564551269554</v>
       </c>
       <c r="W10">
-        <v>0.55246192517510151</v>
+        <v>0.64757973260244162</v>
       </c>
       <c r="X10">
-        <v>0.53588806741984851</v>
+        <v>0.63462813795039275</v>
       </c>
       <c r="Y10">
-        <v>0.519811425397253</v>
+        <v>0.62193557519138487</v>
       </c>
       <c r="Z10">
-        <v>0.50421708263533538</v>
+        <v>0.60949686368755718</v>
       </c>
       <c r="AA10">
-        <v>0.48909057015627533</v>
+        <v>0.59730692641380601</v>
       </c>
       <c r="AB10">
-        <v>0.47441785305158707</v>
+        <v>0.58536078788552992</v>
       </c>
       <c r="AC10">
-        <v>0.46018531746003943</v>
+        <v>0.57365357212781931</v>
       </c>
       <c r="AD10">
-        <v>0.44637975793623824</v>
+        <v>0.56218050068526293</v>
       </c>
       <c r="AE10">
-        <v>0.43298836519815109</v>
+        <v>0.55093689067155771</v>
       </c>
       <c r="AF10">
-        <v>0.41999871424220658</v>
+        <v>0.53991815285812661</v>
       </c>
       <c r="AG10">
-        <v>0.40739875281494037</v>
+        <v>0.52911978980096408</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
@@ -3261,94 +3261,94 @@
         <v>0.97</v>
       </c>
       <c r="D11">
-        <v>0.96514999999999995</v>
+        <v>0.9506</v>
       </c>
       <c r="E11">
-        <v>0.96032424999999999</v>
+        <v>0.93158799999999997</v>
       </c>
       <c r="F11">
-        <v>0.95552262874999994</v>
+        <v>0.91295623999999997</v>
       </c>
       <c r="G11">
-        <v>0.95074501560624991</v>
+        <v>0.89469711519999995</v>
       </c>
       <c r="H11">
-        <v>0.94599129052821862</v>
+        <v>0.87680317289599996</v>
       </c>
       <c r="I11">
-        <v>0.94126133407557755</v>
+        <v>0.85926710943807993</v>
       </c>
       <c r="J11">
-        <v>0.93655502740519969</v>
+        <v>0.84208176724931838</v>
       </c>
       <c r="K11">
-        <v>0.93187225226817372</v>
+        <v>0.82524013190433199</v>
       </c>
       <c r="L11">
-        <v>0.9272128910068328</v>
+        <v>0.80873532926624536</v>
       </c>
       <c r="M11">
-        <v>0.92257682655179862</v>
+        <v>0.79256062268092042</v>
       </c>
       <c r="N11">
-        <v>0.91796394241903967</v>
+        <v>0.776709410227302</v>
       </c>
       <c r="O11">
-        <v>0.91337412270694451</v>
+        <v>0.761175222022756</v>
       </c>
       <c r="P11">
-        <v>0.90880725209340985</v>
+        <v>0.74595171758230083</v>
       </c>
       <c r="Q11">
-        <v>0.90426321583294278</v>
+        <v>0.73103268323065485</v>
       </c>
       <c r="R11">
-        <v>0.89974189975377805</v>
+        <v>0.71641202956604177</v>
       </c>
       <c r="S11">
-        <v>0.8952431902550092</v>
+        <v>0.7020837889747209</v>
       </c>
       <c r="T11">
-        <v>0.89076697430373419</v>
+        <v>0.68804211319522646</v>
       </c>
       <c r="U11">
-        <v>0.88631313943221557</v>
+        <v>0.67428127093132195</v>
       </c>
       <c r="V11">
-        <v>0.88188157373505449</v>
+        <v>0.66079564551269554</v>
       </c>
       <c r="W11">
-        <v>0.87747216586637922</v>
+        <v>0.64757973260244162</v>
       </c>
       <c r="X11">
-        <v>0.87308480503704733</v>
+        <v>0.63462813795039275</v>
       </c>
       <c r="Y11">
-        <v>0.86871938101186208</v>
+        <v>0.62193557519138487</v>
       </c>
       <c r="Z11">
-        <v>0.86437578410680271</v>
+        <v>0.60949686368755718</v>
       </c>
       <c r="AA11">
-        <v>0.86005390518626867</v>
+        <v>0.59730692641380601</v>
       </c>
       <c r="AB11">
-        <v>0.85575363566033735</v>
+        <v>0.58536078788552992</v>
       </c>
       <c r="AC11">
-        <v>0.85147486748203571</v>
+        <v>0.57365357212781931</v>
       </c>
       <c r="AD11">
-        <v>0.84721749314462558</v>
+        <v>0.56218050068526293</v>
       </c>
       <c r="AE11">
-        <v>0.84298140567890245</v>
+        <v>0.55093689067155771</v>
       </c>
       <c r="AF11">
-        <v>0.8387664986505079</v>
+        <v>0.53991815285812661</v>
       </c>
       <c r="AG11">
-        <v>0.83457266615725534</v>
+        <v>0.52911978980096408</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
@@ -3564,94 +3564,94 @@
         <v>0.97</v>
       </c>
       <c r="D14">
-        <v>0.96029999999999993</v>
+        <v>0.9506</v>
       </c>
       <c r="E14">
-        <v>0.9506969999999999</v>
+        <v>0.93158799999999997</v>
       </c>
       <c r="F14">
-        <v>0.9411900299999999</v>
+        <v>0.91295623999999997</v>
       </c>
       <c r="G14">
-        <v>0.93177812969999985</v>
+        <v>0.89469711519999995</v>
       </c>
       <c r="H14">
-        <v>0.92246034840299984</v>
+        <v>0.87680317289599996</v>
       </c>
       <c r="I14">
-        <v>0.91323574491896986</v>
+        <v>0.85926710943807993</v>
       </c>
       <c r="J14">
-        <v>0.90410338746978014</v>
+        <v>0.84208176724931838</v>
       </c>
       <c r="K14">
-        <v>0.89506235359508235</v>
+        <v>0.82524013190433199</v>
       </c>
       <c r="L14">
-        <v>0.88611173005913157</v>
+        <v>0.80873532926624536</v>
       </c>
       <c r="M14">
-        <v>0.87725061275854022</v>
+        <v>0.79256062268092042</v>
       </c>
       <c r="N14">
-        <v>0.86847810663095482</v>
+        <v>0.776709410227302</v>
       </c>
       <c r="O14">
-        <v>0.85979332556464527</v>
+        <v>0.761175222022756</v>
       </c>
       <c r="P14">
-        <v>0.85119539230899877</v>
+        <v>0.74595171758230083</v>
       </c>
       <c r="Q14">
-        <v>0.84268343838590876</v>
+        <v>0.73103268323065485</v>
       </c>
       <c r="R14">
-        <v>0.83425660400204971</v>
+        <v>0.71641202956604177</v>
       </c>
       <c r="S14">
-        <v>0.82591403796202922</v>
+        <v>0.7020837889747209</v>
       </c>
       <c r="T14">
-        <v>0.81765489758240895</v>
+        <v>0.68804211319522646</v>
       </c>
       <c r="U14">
-        <v>0.80947834860658485</v>
+        <v>0.67428127093132195</v>
       </c>
       <c r="V14">
-        <v>0.801383565120519</v>
+        <v>0.66079564551269554</v>
       </c>
       <c r="W14">
-        <v>0.79336972946931383</v>
+        <v>0.64757973260244162</v>
       </c>
       <c r="X14">
-        <v>0.78543603217462066</v>
+        <v>0.63462813795039275</v>
       </c>
       <c r="Y14">
-        <v>0.77758167185287441</v>
+        <v>0.62193557519138487</v>
       </c>
       <c r="Z14">
-        <v>0.76980585513434563</v>
+        <v>0.60949686368755718</v>
       </c>
       <c r="AA14">
-        <v>0.76210779658300221</v>
+        <v>0.59730692641380601</v>
       </c>
       <c r="AB14">
-        <v>0.7544867186171722</v>
+        <v>0.58536078788552992</v>
       </c>
       <c r="AC14">
-        <v>0.74694185143100045</v>
+        <v>0.57365357212781931</v>
       </c>
       <c r="AD14">
-        <v>0.7394724329166904</v>
+        <v>0.56218050068526293</v>
       </c>
       <c r="AE14">
-        <v>0.73207770858752352</v>
+        <v>0.55093689067155771</v>
       </c>
       <c r="AF14">
-        <v>0.72475693150164833</v>
+        <v>0.53991815285812661</v>
       </c>
       <c r="AG14">
-        <v>0.71750936218663186</v>
+        <v>0.52911978980096408</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
@@ -3766,94 +3766,94 @@
         <v>0.97</v>
       </c>
       <c r="D16">
-        <v>0.95545000000000002</v>
+        <v>0.9506</v>
       </c>
       <c r="E16">
-        <v>0.94111825000000005</v>
+        <v>0.93158799999999997</v>
       </c>
       <c r="F16">
-        <v>0.92700147625000007</v>
+        <v>0.91295623999999997</v>
       </c>
       <c r="G16">
-        <v>0.91309645410625007</v>
+        <v>0.89469711519999995</v>
       </c>
       <c r="H16">
-        <v>0.8994000072946563</v>
+        <v>0.87680317289599996</v>
       </c>
       <c r="I16">
-        <v>0.88590900718523646</v>
+        <v>0.85926710943807993</v>
       </c>
       <c r="J16">
-        <v>0.87262037207745791</v>
+        <v>0.84208176724931838</v>
       </c>
       <c r="K16">
-        <v>0.85953106649629607</v>
+        <v>0.82524013190433199</v>
       </c>
       <c r="L16">
-        <v>0.84663810049885158</v>
+        <v>0.80873532926624536</v>
       </c>
       <c r="M16">
-        <v>0.83393852899136878</v>
+        <v>0.79256062268092042</v>
       </c>
       <c r="N16">
-        <v>0.82142945105649823</v>
+        <v>0.776709410227302</v>
       </c>
       <c r="O16">
-        <v>0.80910800929065074</v>
+        <v>0.761175222022756</v>
       </c>
       <c r="P16">
-        <v>0.79697138915129095</v>
+        <v>0.74595171758230083</v>
       </c>
       <c r="Q16">
-        <v>0.78501681831402159</v>
+        <v>0.73103268323065485</v>
       </c>
       <c r="R16">
-        <v>0.77324156603931127</v>
+        <v>0.71641202956604177</v>
       </c>
       <c r="S16">
-        <v>0.76164294254872156</v>
+        <v>0.7020837889747209</v>
       </c>
       <c r="T16">
-        <v>0.7502182984104907</v>
+        <v>0.68804211319522646</v>
       </c>
       <c r="U16">
-        <v>0.73896502393433339</v>
+        <v>0.67428127093132195</v>
       </c>
       <c r="V16">
-        <v>0.72788054857531836</v>
+        <v>0.66079564551269554</v>
       </c>
       <c r="W16">
-        <v>0.7169623403466886</v>
+        <v>0.64757973260244162</v>
       </c>
       <c r="X16">
-        <v>0.70620790524148824</v>
+        <v>0.63462813795039275</v>
       </c>
       <c r="Y16">
-        <v>0.69561478666286591</v>
+        <v>0.62193557519138487</v>
       </c>
       <c r="Z16">
-        <v>0.68518056486292289</v>
+        <v>0.60949686368755718</v>
       </c>
       <c r="AA16">
-        <v>0.67490285638997904</v>
+        <v>0.59730692641380601</v>
       </c>
       <c r="AB16">
-        <v>0.66477931354412934</v>
+        <v>0.58536078788552992</v>
       </c>
       <c r="AC16">
-        <v>0.65480762384096736</v>
+        <v>0.57365357212781931</v>
       </c>
       <c r="AD16">
-        <v>0.64498550948335287</v>
+        <v>0.56218050068526293</v>
       </c>
       <c r="AE16">
-        <v>0.63531072684110257</v>
+        <v>0.55093689067155771</v>
       </c>
       <c r="AF16">
-        <v>0.62578106593848604</v>
+        <v>0.53991815285812661</v>
       </c>
       <c r="AG16">
-        <v>0.61639434994940878</v>
+        <v>0.52911978980096408</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
@@ -3968,94 +3968,94 @@
         <v>0.97</v>
       </c>
       <c r="D18">
-        <v>0.94574999999999998</v>
+        <v>0.9506</v>
       </c>
       <c r="E18">
-        <v>0.92210625000000002</v>
+        <v>0.93158799999999997</v>
       </c>
       <c r="F18">
-        <v>0.89905359375000005</v>
+        <v>0.91295623999999997</v>
       </c>
       <c r="G18">
-        <v>0.87657725390625008</v>
+        <v>0.89469711519999995</v>
       </c>
       <c r="H18">
-        <v>0.85466282255859383</v>
+        <v>0.87680317289599996</v>
       </c>
       <c r="I18">
-        <v>0.83329625199462898</v>
+        <v>0.85926710943807993</v>
       </c>
       <c r="J18">
-        <v>0.81246384569476326</v>
+        <v>0.84208176724931838</v>
       </c>
       <c r="K18">
-        <v>0.79215224955239416</v>
+        <v>0.82524013190433199</v>
       </c>
       <c r="L18">
-        <v>0.77234844331358432</v>
+        <v>0.80873532926624536</v>
       </c>
       <c r="M18">
-        <v>0.75303973223074472</v>
+        <v>0.79256062268092042</v>
       </c>
       <c r="N18">
-        <v>0.7342137389249761</v>
+        <v>0.776709410227302</v>
       </c>
       <c r="O18">
-        <v>0.7158583954518517</v>
+        <v>0.761175222022756</v>
       </c>
       <c r="P18">
-        <v>0.69796193556555541</v>
+        <v>0.74595171758230083</v>
       </c>
       <c r="Q18">
-        <v>0.68051288717641656</v>
+        <v>0.73103268323065485</v>
       </c>
       <c r="R18">
-        <v>0.6635000649970062</v>
+        <v>0.71641202956604177</v>
       </c>
       <c r="S18">
-        <v>0.64691256337208103</v>
+        <v>0.7020837889747209</v>
       </c>
       <c r="T18">
-        <v>0.63073974928777898</v>
+        <v>0.68804211319522646</v>
       </c>
       <c r="U18">
-        <v>0.61497125555558452</v>
+        <v>0.67428127093132195</v>
       </c>
       <c r="V18">
-        <v>0.59959697416669488</v>
+        <v>0.66079564551269554</v>
       </c>
       <c r="W18">
-        <v>0.58460704981252753</v>
+        <v>0.64757973260244162</v>
       </c>
       <c r="X18">
-        <v>0.56999187356721437</v>
+        <v>0.63462813795039275</v>
       </c>
       <c r="Y18">
-        <v>0.555742076728034</v>
+        <v>0.62193557519138487</v>
       </c>
       <c r="Z18">
-        <v>0.54184852480983314</v>
+        <v>0.60949686368755718</v>
       </c>
       <c r="AA18">
-        <v>0.5283023116895873</v>
+        <v>0.59730692641380601</v>
       </c>
       <c r="AB18">
-        <v>0.5150947538973476</v>
+        <v>0.58536078788552992</v>
       </c>
       <c r="AC18">
-        <v>0.50221738504991387</v>
+        <v>0.57365357212781931</v>
       </c>
       <c r="AD18">
-        <v>0.489661950423666</v>
+        <v>0.56218050068526293</v>
       </c>
       <c r="AE18">
-        <v>0.47742040166307437</v>
+        <v>0.55093689067155771</v>
       </c>
       <c r="AF18">
-        <v>0.46548489162149753</v>
+        <v>0.53991815285812661</v>
       </c>
       <c r="AG18">
-        <v>0.4538477693309601</v>
+        <v>0.52911978980096408</v>
       </c>
     </row>
   </sheetData>

--- a/2.RD_CGE/Input_w-t/Projection.xlsx
+++ b/2.RD_CGE/Input_w-t/Projection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_w-t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1D908C-F777-4C5D-8558-5DBAD3F6C8FD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBF84D1-0856-45DD-A072-6DD64FC27F77}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="870" activeTab="9" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="870" activeTab="11" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseyear" sheetId="12" r:id="rId1"/>
@@ -6432,128 +6432,101 @@
         <v>0</v>
       </c>
       <c r="C2" s="13">
-        <v>3.3333333333333326E-2</v>
+        <v>3.3333300000000003E-2</v>
       </c>
       <c r="D2" s="13">
-        <v>6.6666666666666666E-2</v>
+        <v>6.6666699999999954E-2</v>
       </c>
       <c r="E2" s="13">
-        <v>0.10000000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="F2" s="13">
-        <f>E2+$AI2</f>
-        <v>0.11071428571428574</v>
+        <v>0.11428571428571428</v>
       </c>
       <c r="G2" s="13">
-        <f>F2+$AI2</f>
-        <v>0.12142857142857146</v>
+        <v>0.12857142857142856</v>
       </c>
       <c r="H2" s="13">
-        <f t="shared" ref="H2:AE2" si="0">G2+$AI2</f>
-        <v>0.13214285714285717</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="I2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714288</v>
+        <v>0.15714285714285714</v>
       </c>
       <c r="J2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.15357142857142858</v>
+        <v>0.17142857142857143</v>
       </c>
       <c r="K2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.16428571428571428</v>
+        <v>0.18571428571428572</v>
       </c>
       <c r="L2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="M2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.18571428571428569</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="N2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.1964285714285714</v>
+        <v>0.22857142857142856</v>
       </c>
       <c r="O2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.2071428571428571</v>
+        <v>0.24285714285714285</v>
       </c>
       <c r="P2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.2178571428571428</v>
+        <v>0.25714285714285712</v>
       </c>
       <c r="Q2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.22857142857142851</v>
+        <v>0.27142857142857146</v>
       </c>
       <c r="R2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.23928571428571421</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.24999999999999992</v>
+        <v>0.3</v>
       </c>
       <c r="T2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.26071428571428562</v>
+        <v>0.31428571428571428</v>
       </c>
       <c r="U2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.27142857142857135</v>
+        <v>0.32857142857142857</v>
       </c>
       <c r="V2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.28214285714285708</v>
+        <v>0.34285714285714286</v>
       </c>
       <c r="W2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.29285714285714282</v>
+        <v>0.3571428571428571</v>
       </c>
       <c r="X2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.30357142857142855</v>
+        <v>0.37142857142857144</v>
       </c>
       <c r="Y2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.31428571428571428</v>
+        <v>0.38571428571428568</v>
       </c>
       <c r="Z2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.32500000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="AA2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.33571428571428574</v>
+        <v>0.41428571428571426</v>
       </c>
       <c r="AB2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.34642857142857147</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="AC2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.35714285714285721</v>
+        <v>0.44285714285714284</v>
       </c>
       <c r="AD2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.36785714285714294</v>
+        <v>0.45714285714285718</v>
       </c>
       <c r="AE2" s="13">
-        <f t="shared" si="0"/>
-        <v>0.37857142857142867</v>
+        <v>0.47142857142857142</v>
       </c>
       <c r="AF2" s="13">
-        <f t="shared" ref="AF2" si="1">AE2+$AI2</f>
-        <v>0.3892857142857144</v>
+        <v>0.48571428571428565</v>
       </c>
       <c r="AG2" s="13">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AI2" s="28">
         <f>(AG2-E2)/$AI$1</f>
-        <v>1.0714285714285714E-2</v>
+        <v>1.4285714285714287E-2</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
@@ -6573,118 +6546,118 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="F3" s="13">
-        <f t="shared" ref="F3:F18" si="2">E3+$AI3</f>
+        <f t="shared" ref="F3:F18" si="0">E3+$AI3</f>
         <v>5.5357142857142869E-2</v>
       </c>
       <c r="G3" s="13">
-        <f t="shared" ref="G3:G18" si="3">F3+$AI3</f>
+        <f t="shared" ref="G3:G18" si="1">F3+$AI3</f>
         <v>6.0714285714285728E-2</v>
       </c>
       <c r="H3" s="13">
-        <f t="shared" ref="H3:AE3" si="4">G3+$AI3</f>
+        <f t="shared" ref="H3:AE3" si="2">G3+$AI3</f>
         <v>6.6071428571428586E-2</v>
       </c>
       <c r="I3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>7.1428571428571438E-2</v>
       </c>
       <c r="J3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>7.678571428571429E-2</v>
       </c>
       <c r="K3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>8.2142857142857142E-2</v>
       </c>
       <c r="L3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>8.7499999999999994E-2</v>
       </c>
       <c r="M3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>9.2857142857142846E-2</v>
       </c>
       <c r="N3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>9.8214285714285698E-2</v>
       </c>
       <c r="O3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.10357142857142855</v>
       </c>
       <c r="P3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.1089285714285714</v>
       </c>
       <c r="Q3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.11428571428571425</v>
       </c>
       <c r="R3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.11964285714285711</v>
       </c>
       <c r="S3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.12499999999999996</v>
       </c>
       <c r="T3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.13035714285714281</v>
       </c>
       <c r="U3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.13571428571428568</v>
       </c>
       <c r="V3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.14107142857142854</v>
       </c>
       <c r="W3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.14642857142857141</v>
       </c>
       <c r="X3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.15178571428571427</v>
       </c>
       <c r="Y3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.15714285714285714</v>
       </c>
       <c r="Z3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.16250000000000001</v>
       </c>
       <c r="AA3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.16785714285714287</v>
       </c>
       <c r="AB3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.17321428571428574</v>
       </c>
       <c r="AC3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.1785714285714286</v>
       </c>
       <c r="AD3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.18392857142857147</v>
       </c>
       <c r="AE3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.18928571428571433</v>
       </c>
       <c r="AF3" s="13">
-        <f t="shared" ref="AF3" si="5">AE3+$AI3</f>
+        <f t="shared" ref="AF3" si="3">AE3+$AI3</f>
         <v>0.1946428571428572</v>
       </c>
       <c r="AG3" s="13">
         <v>0.2</v>
       </c>
       <c r="AI3" s="28">
-        <f t="shared" ref="AI3:AI18" si="6">(AG3-E3)/$AI$1</f>
+        <f t="shared" ref="AI3:AI18" si="4">(AG3-E3)/$AI$1</f>
         <v>5.3571428571428572E-3</v>
       </c>
     </row>
@@ -6705,118 +6678,118 @@
         <v>0.10000000000000002</v>
       </c>
       <c r="F4" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.11071428571428574</v>
       </c>
       <c r="G4" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.12142857142857146</v>
       </c>
       <c r="H4" s="13">
-        <f t="shared" ref="H4:AE4" si="7">G4+$AI4</f>
+        <f t="shared" ref="H4:AE4" si="5">G4+$AI4</f>
         <v>0.13214285714285717</v>
       </c>
       <c r="I4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.14285714285714288</v>
       </c>
       <c r="J4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.15357142857142858</v>
       </c>
       <c r="K4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.16428571428571428</v>
       </c>
       <c r="L4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.17499999999999999</v>
       </c>
       <c r="M4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.18571428571428569</v>
       </c>
       <c r="N4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.1964285714285714</v>
       </c>
       <c r="O4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.2071428571428571</v>
       </c>
       <c r="P4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.2178571428571428</v>
       </c>
       <c r="Q4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.22857142857142851</v>
       </c>
       <c r="R4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.23928571428571421</v>
       </c>
       <c r="S4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.24999999999999992</v>
       </c>
       <c r="T4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.26071428571428562</v>
       </c>
       <c r="U4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.27142857142857135</v>
       </c>
       <c r="V4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.28214285714285708</v>
       </c>
       <c r="W4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.29285714285714282</v>
       </c>
       <c r="X4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.30357142857142855</v>
       </c>
       <c r="Y4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.31428571428571428</v>
       </c>
       <c r="Z4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="AA4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.33571428571428574</v>
       </c>
       <c r="AB4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.34642857142857147</v>
       </c>
       <c r="AC4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.35714285714285721</v>
       </c>
       <c r="AD4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.36785714285714294</v>
       </c>
       <c r="AE4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.37857142857142867</v>
       </c>
       <c r="AF4" s="13">
-        <f t="shared" ref="AF4" si="8">AE4+$AI4</f>
+        <f t="shared" ref="AF4" si="6">AE4+$AI4</f>
         <v>0.3892857142857144</v>
       </c>
       <c r="AG4" s="13">
         <v>0.4</v>
       </c>
       <c r="AI4" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>1.0714285714285714E-2</v>
       </c>
     </row>
@@ -6837,118 +6810,118 @@
         <v>0.01</v>
       </c>
       <c r="F5" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G5" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H5" s="13">
-        <f t="shared" ref="H5:AE6" si="9">G5+$AI5</f>
+        <f t="shared" ref="H5:AE6" si="7">G5+$AI5</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE5" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF5" s="13">
-        <f t="shared" ref="AF5:AF6" si="10">AE5+$AI5</f>
+        <f t="shared" ref="AF5:AF6" si="8">AE5+$AI5</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG5" s="13">
         <v>0.1</v>
       </c>
       <c r="AI5" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -6971,118 +6944,118 @@
         <v>1E-4</v>
       </c>
       <c r="F6" s="32">
-        <f t="shared" ref="F6" si="11">E6+$AI6</f>
+        <f t="shared" ref="F6" si="9">E6+$AI6</f>
         <v>1.3214285714285715E-4</v>
       </c>
       <c r="G6" s="32">
-        <f t="shared" ref="G6" si="12">F6+$AI6</f>
+        <f t="shared" ref="G6" si="10">F6+$AI6</f>
         <v>1.6428571428571431E-4</v>
       </c>
       <c r="H6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1.9642857142857146E-4</v>
       </c>
       <c r="I6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.2857142857142862E-4</v>
       </c>
       <c r="J6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.6071428571428578E-4</v>
       </c>
       <c r="K6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.9285714285714294E-4</v>
       </c>
       <c r="L6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.2500000000000009E-4</v>
       </c>
       <c r="M6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.5714285714285725E-4</v>
       </c>
       <c r="N6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.8928571428571441E-4</v>
       </c>
       <c r="O6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4.2142857142857157E-4</v>
       </c>
       <c r="P6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4.5357142857142872E-4</v>
       </c>
       <c r="Q6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4.8571428571428588E-4</v>
       </c>
       <c r="R6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.1785714285714304E-4</v>
       </c>
       <c r="S6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.5000000000000014E-4</v>
       </c>
       <c r="T6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.8214285714285724E-4</v>
       </c>
       <c r="U6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.1428571428571435E-4</v>
       </c>
       <c r="V6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.4642857142857145E-4</v>
       </c>
       <c r="W6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.7857142857142855E-4</v>
       </c>
       <c r="X6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7.1071428571428566E-4</v>
       </c>
       <c r="Y6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7.4285714285714276E-4</v>
       </c>
       <c r="Z6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7.7499999999999986E-4</v>
       </c>
       <c r="AA6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.0714285714285697E-4</v>
       </c>
       <c r="AB6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.3928571428571407E-4</v>
       </c>
       <c r="AC6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.7142857142857117E-4</v>
       </c>
       <c r="AD6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>9.0357142857142828E-4</v>
       </c>
       <c r="AE6" s="32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>9.3571428571428538E-4</v>
       </c>
       <c r="AF6" s="32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>9.6785714285714248E-4</v>
       </c>
       <c r="AG6" s="32">
         <v>1E-3</v>
       </c>
       <c r="AI6" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3.2142857142857144E-5</v>
       </c>
     </row>
@@ -7105,118 +7078,118 @@
         <v>1E-4</v>
       </c>
       <c r="F7" s="32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.3214285714285715E-4</v>
       </c>
       <c r="G7" s="32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.6428571428571431E-4</v>
       </c>
       <c r="H7" s="32">
-        <f t="shared" ref="H7:AE7" si="13">G7+$AI7</f>
+        <f t="shared" ref="H7:AE7" si="11">G7+$AI7</f>
         <v>1.9642857142857146E-4</v>
       </c>
       <c r="I7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>2.2857142857142862E-4</v>
       </c>
       <c r="J7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>2.6071428571428578E-4</v>
       </c>
       <c r="K7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>2.9285714285714294E-4</v>
       </c>
       <c r="L7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>3.2500000000000009E-4</v>
       </c>
       <c r="M7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>3.5714285714285725E-4</v>
       </c>
       <c r="N7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>3.8928571428571441E-4</v>
       </c>
       <c r="O7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>4.2142857142857157E-4</v>
       </c>
       <c r="P7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>4.5357142857142872E-4</v>
       </c>
       <c r="Q7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>4.8571428571428588E-4</v>
       </c>
       <c r="R7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>5.1785714285714304E-4</v>
       </c>
       <c r="S7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>5.5000000000000014E-4</v>
       </c>
       <c r="T7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>5.8214285714285724E-4</v>
       </c>
       <c r="U7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>6.1428571428571435E-4</v>
       </c>
       <c r="V7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>6.4642857142857145E-4</v>
       </c>
       <c r="W7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>6.7857142857142855E-4</v>
       </c>
       <c r="X7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>7.1071428571428566E-4</v>
       </c>
       <c r="Y7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>7.4285714285714276E-4</v>
       </c>
       <c r="Z7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>7.7499999999999986E-4</v>
       </c>
       <c r="AA7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>8.0714285714285697E-4</v>
       </c>
       <c r="AB7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>8.3928571428571407E-4</v>
       </c>
       <c r="AC7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>8.7142857142857117E-4</v>
       </c>
       <c r="AD7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>9.0357142857142828E-4</v>
       </c>
       <c r="AE7" s="32">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>9.3571428571428538E-4</v>
       </c>
       <c r="AF7" s="32">
-        <f t="shared" ref="AF7" si="14">AE7+$AI7</f>
+        <f t="shared" ref="AF7" si="12">AE7+$AI7</f>
         <v>9.6785714285714248E-4</v>
       </c>
       <c r="AG7" s="32">
         <v>1E-3</v>
       </c>
       <c r="AI7" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3.2142857142857144E-5</v>
       </c>
     </row>
@@ -7237,118 +7210,118 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="F8" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.22142857142857147</v>
       </c>
       <c r="G8" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.24285714285714291</v>
       </c>
       <c r="H8" s="13">
-        <f t="shared" ref="H8:AE8" si="15">G8+$AI8</f>
+        <f t="shared" ref="H8:AE8" si="13">G8+$AI8</f>
         <v>0.26428571428571435</v>
       </c>
       <c r="I8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.28571428571428575</v>
       </c>
       <c r="J8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.30714285714285716</v>
       </c>
       <c r="K8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.32857142857142857</v>
       </c>
       <c r="L8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.35</v>
       </c>
       <c r="M8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.37142857142857139</v>
       </c>
       <c r="N8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.39285714285714279</v>
       </c>
       <c r="O8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.4142857142857142</v>
       </c>
       <c r="P8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.43571428571428561</v>
       </c>
       <c r="Q8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.45714285714285702</v>
       </c>
       <c r="R8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.47857142857142843</v>
       </c>
       <c r="S8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.49999999999999983</v>
       </c>
       <c r="T8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.52142857142857124</v>
       </c>
       <c r="U8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.5428571428571427</v>
       </c>
       <c r="V8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.56428571428571417</v>
       </c>
       <c r="W8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.58571428571428563</v>
       </c>
       <c r="X8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.6071428571428571</v>
       </c>
       <c r="Y8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.62857142857142856</v>
       </c>
       <c r="Z8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.65</v>
       </c>
       <c r="AA8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.67142857142857149</v>
       </c>
       <c r="AB8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.69285714285714295</v>
       </c>
       <c r="AC8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.71428571428571441</v>
       </c>
       <c r="AD8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.73571428571428588</v>
       </c>
       <c r="AE8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.75714285714285734</v>
       </c>
       <c r="AF8" s="13">
-        <f t="shared" ref="AF8" si="16">AE8+$AI8</f>
+        <f t="shared" ref="AF8" si="14">AE8+$AI8</f>
         <v>0.7785714285714288</v>
       </c>
       <c r="AG8" s="13">
         <v>0.8</v>
       </c>
       <c r="AI8" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2.1428571428571429E-2</v>
       </c>
     </row>
@@ -7369,118 +7342,118 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="F9" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>5.5357142857142869E-2</v>
       </c>
       <c r="G9" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>6.0714285714285728E-2</v>
       </c>
       <c r="H9" s="13">
-        <f t="shared" ref="H9:AE9" si="17">G9+$AI9</f>
+        <f t="shared" ref="H9:AE9" si="15">G9+$AI9</f>
         <v>6.6071428571428586E-2</v>
       </c>
       <c r="I9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>7.1428571428571438E-2</v>
       </c>
       <c r="J9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>7.678571428571429E-2</v>
       </c>
       <c r="K9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>8.2142857142857142E-2</v>
       </c>
       <c r="L9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>8.7499999999999994E-2</v>
       </c>
       <c r="M9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>9.2857142857142846E-2</v>
       </c>
       <c r="N9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>9.8214285714285698E-2</v>
       </c>
       <c r="O9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.10357142857142855</v>
       </c>
       <c r="P9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.1089285714285714</v>
       </c>
       <c r="Q9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.11428571428571425</v>
       </c>
       <c r="R9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.11964285714285711</v>
       </c>
       <c r="S9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.12499999999999996</v>
       </c>
       <c r="T9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.13035714285714281</v>
       </c>
       <c r="U9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.13571428571428568</v>
       </c>
       <c r="V9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.14107142857142854</v>
       </c>
       <c r="W9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.14642857142857141</v>
       </c>
       <c r="X9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.15178571428571427</v>
       </c>
       <c r="Y9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.15714285714285714</v>
       </c>
       <c r="Z9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.16250000000000001</v>
       </c>
       <c r="AA9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.16785714285714287</v>
       </c>
       <c r="AB9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.17321428571428574</v>
       </c>
       <c r="AC9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.1785714285714286</v>
       </c>
       <c r="AD9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.18392857142857147</v>
       </c>
       <c r="AE9" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.18928571428571433</v>
       </c>
       <c r="AF9" s="13">
-        <f t="shared" ref="AF9" si="18">AE9+$AI9</f>
+        <f t="shared" ref="AF9" si="16">AE9+$AI9</f>
         <v>0.1946428571428572</v>
       </c>
       <c r="AG9" s="13">
         <v>0.2</v>
       </c>
       <c r="AI9" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5.3571428571428572E-3</v>
       </c>
     </row>
@@ -7501,118 +7474,118 @@
         <v>0.40000000000000008</v>
       </c>
       <c r="F10" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.44285714285714295</v>
       </c>
       <c r="G10" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.48571428571428582</v>
       </c>
       <c r="H10" s="13">
-        <f t="shared" ref="H10:AE10" si="19">G10+$AI10</f>
+        <f t="shared" ref="H10:AE10" si="17">G10+$AI10</f>
         <v>0.52857142857142869</v>
       </c>
       <c r="I10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.57142857142857151</v>
       </c>
       <c r="J10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.61428571428571432</v>
       </c>
       <c r="K10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.65714285714285714</v>
       </c>
       <c r="L10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="M10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.74285714285714277</v>
       </c>
       <c r="N10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.78571428571428559</v>
       </c>
       <c r="O10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.8285714285714284</v>
       </c>
       <c r="P10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.87142857142857122</v>
       </c>
       <c r="Q10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.91428571428571404</v>
       </c>
       <c r="R10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.95714285714285685</v>
       </c>
       <c r="S10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.99999999999999967</v>
       </c>
       <c r="T10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.0428571428571425</v>
       </c>
       <c r="U10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.0857142857142854</v>
       </c>
       <c r="V10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.1285714285714283</v>
       </c>
       <c r="W10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.1714285714285713</v>
       </c>
       <c r="X10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="Y10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.2571428571428571</v>
       </c>
       <c r="Z10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.3</v>
       </c>
       <c r="AA10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.342857142857143</v>
       </c>
       <c r="AB10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.3857142857142859</v>
       </c>
       <c r="AC10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.4285714285714288</v>
       </c>
       <c r="AD10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.4714285714285718</v>
       </c>
       <c r="AE10" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1.5142857142857147</v>
       </c>
       <c r="AF10" s="13">
-        <f t="shared" ref="AF10" si="20">AE10+$AI10</f>
+        <f t="shared" ref="AF10" si="18">AE10+$AI10</f>
         <v>1.5571428571428576</v>
       </c>
       <c r="AG10" s="13">
         <v>1.6</v>
       </c>
       <c r="AI10" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4.2857142857142858E-2</v>
       </c>
     </row>
@@ -7633,118 +7606,118 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="F11" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>5.5357142857142869E-2</v>
       </c>
       <c r="G11" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>6.0714285714285728E-2</v>
       </c>
       <c r="H11" s="13">
-        <f t="shared" ref="H11:AE11" si="21">G11+$AI11</f>
+        <f t="shared" ref="H11:AE11" si="19">G11+$AI11</f>
         <v>6.6071428571428586E-2</v>
       </c>
       <c r="I11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>7.1428571428571438E-2</v>
       </c>
       <c r="J11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>7.678571428571429E-2</v>
       </c>
       <c r="K11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>8.2142857142857142E-2</v>
       </c>
       <c r="L11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>8.7499999999999994E-2</v>
       </c>
       <c r="M11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>9.2857142857142846E-2</v>
       </c>
       <c r="N11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>9.8214285714285698E-2</v>
       </c>
       <c r="O11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.10357142857142855</v>
       </c>
       <c r="P11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.1089285714285714</v>
       </c>
       <c r="Q11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.11428571428571425</v>
       </c>
       <c r="R11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.11964285714285711</v>
       </c>
       <c r="S11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.12499999999999996</v>
       </c>
       <c r="T11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.13035714285714281</v>
       </c>
       <c r="U11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.13571428571428568</v>
       </c>
       <c r="V11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.14107142857142854</v>
       </c>
       <c r="W11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.14642857142857141</v>
       </c>
       <c r="X11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.15178571428571427</v>
       </c>
       <c r="Y11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.15714285714285714</v>
       </c>
       <c r="Z11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.16250000000000001</v>
       </c>
       <c r="AA11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.16785714285714287</v>
       </c>
       <c r="AB11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.17321428571428574</v>
       </c>
       <c r="AC11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.1785714285714286</v>
       </c>
       <c r="AD11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.18392857142857147</v>
       </c>
       <c r="AE11" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0.18928571428571433</v>
       </c>
       <c r="AF11" s="13">
-        <f t="shared" ref="AF11" si="22">AE11+$AI11</f>
+        <f t="shared" ref="AF11" si="20">AE11+$AI11</f>
         <v>0.1946428571428572</v>
       </c>
       <c r="AG11" s="13">
         <v>0.2</v>
       </c>
       <c r="AI11" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5.3571428571428572E-3</v>
       </c>
     </row>
@@ -7765,118 +7738,118 @@
         <v>0.01</v>
       </c>
       <c r="F12" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H12" s="13">
-        <f t="shared" ref="H12:AE12" si="23">G12+$AI12</f>
+        <f t="shared" ref="H12:AE12" si="21">G12+$AI12</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE12" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF12" s="13">
-        <f t="shared" ref="AF12" si="24">AE12+$AI12</f>
+        <f t="shared" ref="AF12" si="22">AE12+$AI12</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG12" s="13">
         <v>0.1</v>
       </c>
       <c r="AI12" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -7897,118 +7870,118 @@
         <v>0.01</v>
       </c>
       <c r="F13" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H13" s="13">
-        <f t="shared" ref="H13:AE13" si="25">G13+$AI13</f>
+        <f t="shared" ref="H13:AE13" si="23">G13+$AI13</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE13" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF13" s="13">
-        <f t="shared" ref="AF13" si="26">AE13+$AI13</f>
+        <f t="shared" ref="AF13" si="24">AE13+$AI13</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG13" s="13">
         <v>0.1</v>
       </c>
       <c r="AI13" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -8029,118 +8002,118 @@
         <v>0.01</v>
       </c>
       <c r="F14" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H14" s="13">
-        <f t="shared" ref="H14:AE14" si="27">G14+$AI14</f>
+        <f t="shared" ref="H14:AE14" si="25">G14+$AI14</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE14" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF14" s="13">
-        <f t="shared" ref="AF14" si="28">AE14+$AI14</f>
+        <f t="shared" ref="AF14" si="26">AE14+$AI14</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG14" s="13">
         <v>0.1</v>
       </c>
       <c r="AI14" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -8161,118 +8134,118 @@
         <v>0.01</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" ref="H15:AE15" si="29">G15+$AI15</f>
+        <f t="shared" ref="H15:AE15" si="27">G15+$AI15</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE15" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF15" s="13">
-        <f t="shared" ref="AF15" si="30">AE15+$AI15</f>
+        <f t="shared" ref="AF15" si="28">AE15+$AI15</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG15" s="13">
         <v>0.1</v>
       </c>
       <c r="AI15" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -8293,118 +8266,118 @@
         <v>0.01</v>
       </c>
       <c r="F16" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H16" s="13">
-        <f t="shared" ref="H16:AE16" si="31">G16+$AI16</f>
+        <f t="shared" ref="H16:AE16" si="29">G16+$AI16</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE16" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF16" s="13">
-        <f t="shared" ref="AF16" si="32">AE16+$AI16</f>
+        <f t="shared" ref="AF16" si="30">AE16+$AI16</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG16" s="13">
         <v>0.1</v>
       </c>
       <c r="AI16" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -8425,118 +8398,118 @@
         <v>0.01</v>
       </c>
       <c r="F17" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H17" s="13">
-        <f t="shared" ref="H17:AE17" si="33">G17+$AI17</f>
+        <f t="shared" ref="H17:AE17" si="31">G17+$AI17</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE17" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF17" s="13">
-        <f t="shared" ref="AF17" si="34">AE17+$AI17</f>
+        <f t="shared" ref="AF17" si="32">AE17+$AI17</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG17" s="13">
         <v>0.1</v>
       </c>
       <c r="AI17" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -8557,118 +8530,118 @@
         <v>0.10000000000000002</v>
       </c>
       <c r="F18" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.11071428571428574</v>
       </c>
       <c r="G18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.12142857142857146</v>
       </c>
       <c r="H18" s="13">
-        <f t="shared" ref="H18:AE18" si="35">G18+$AI18</f>
+        <f t="shared" ref="H18:AE18" si="33">G18+$AI18</f>
         <v>0.13214285714285717</v>
       </c>
       <c r="I18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.14285714285714288</v>
       </c>
       <c r="J18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.15357142857142858</v>
       </c>
       <c r="K18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.16428571428571428</v>
       </c>
       <c r="L18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.17499999999999999</v>
       </c>
       <c r="M18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.18571428571428569</v>
       </c>
       <c r="N18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.1964285714285714</v>
       </c>
       <c r="O18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.2071428571428571</v>
       </c>
       <c r="P18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.2178571428571428</v>
       </c>
       <c r="Q18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.22857142857142851</v>
       </c>
       <c r="R18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.23928571428571421</v>
       </c>
       <c r="S18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.24999999999999992</v>
       </c>
       <c r="T18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.26071428571428562</v>
       </c>
       <c r="U18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.27142857142857135</v>
       </c>
       <c r="V18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.28214285714285708</v>
       </c>
       <c r="W18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.29285714285714282</v>
       </c>
       <c r="X18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.30357142857142855</v>
       </c>
       <c r="Y18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.31428571428571428</v>
       </c>
       <c r="Z18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="AA18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.33571428571428574</v>
       </c>
       <c r="AB18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.34642857142857147</v>
       </c>
       <c r="AC18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.35714285714285721</v>
       </c>
       <c r="AD18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.36785714285714294</v>
       </c>
       <c r="AE18" s="13">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0.37857142857142867</v>
       </c>
       <c r="AF18" s="13">
-        <f t="shared" ref="AF18" si="36">AE18+$AI18</f>
+        <f t="shared" ref="AF18" si="34">AE18+$AI18</f>
         <v>0.3892857142857144</v>
       </c>
       <c r="AG18" s="13">
         <v>0.4</v>
       </c>
       <c r="AI18" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>1.0714285714285714E-2</v>
       </c>
     </row>

--- a/2.RD_CGE/Input_w-t/Projection.xlsx
+++ b/2.RD_CGE/Input_w-t/Projection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_w-t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBF84D1-0856-45DD-A072-6DD64FC27F77}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DD9A0F-22F2-45AE-8CB7-D3FC552A8E39}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="870" activeTab="11" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="870" activeTab="13" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseyear" sheetId="12" r:id="rId1"/>
@@ -23,14 +23,15 @@
     <sheet name="AEEI_low" sheetId="22" r:id="rId8"/>
     <sheet name="AEEI_high" sheetId="11" r:id="rId9"/>
     <sheet name="TREND" sheetId="18" r:id="rId10"/>
-    <sheet name="CTAX_Cal" sheetId="23" r:id="rId11"/>
-    <sheet name="CTAX_CPS" sheetId="24" r:id="rId12"/>
-    <sheet name="CTAX_NZS" sheetId="25" r:id="rId13"/>
-    <sheet name="CTAX_61" sheetId="17" r:id="rId14"/>
-    <sheet name="CTAX_145" sheetId="13" r:id="rId15"/>
-    <sheet name="CTAX_285" sheetId="14" r:id="rId16"/>
-    <sheet name="CTAX_425" sheetId="15" r:id="rId17"/>
-    <sheet name="CTAX_565" sheetId="16" r:id="rId18"/>
+    <sheet name="TREND2" sheetId="26" r:id="rId11"/>
+    <sheet name="CTAX_Cal" sheetId="23" r:id="rId12"/>
+    <sheet name="CTAX_CPS" sheetId="24" r:id="rId13"/>
+    <sheet name="CTAX_NZS" sheetId="25" r:id="rId14"/>
+    <sheet name="CTAX_61" sheetId="17" r:id="rId15"/>
+    <sheet name="CTAX_145" sheetId="13" r:id="rId16"/>
+    <sheet name="CTAX_285" sheetId="14" r:id="rId17"/>
+    <sheet name="CTAX_425" sheetId="15" r:id="rId18"/>
+    <sheet name="CTAX_565" sheetId="16" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">GDP_Projection!$A$1:$CF$18</definedName>
@@ -80,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="88">
   <si>
     <t>01_KOR</t>
   </si>
@@ -456,7 +457,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -503,22 +504,23 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4064,6 +4066,1832 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5A193B-B5D4-4AC5-97E6-556CD0293688}">
+  <dimension ref="A1:AG18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="14">
+        <v>2019</v>
+      </c>
+      <c r="C1" s="14">
+        <v>2020</v>
+      </c>
+      <c r="D1" s="14">
+        <v>2021</v>
+      </c>
+      <c r="E1" s="14">
+        <v>2022</v>
+      </c>
+      <c r="F1" s="14">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="14">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="14">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="14">
+        <v>2026</v>
+      </c>
+      <c r="J1" s="14">
+        <v>2027</v>
+      </c>
+      <c r="K1" s="14">
+        <v>2028</v>
+      </c>
+      <c r="L1" s="14">
+        <v>2029</v>
+      </c>
+      <c r="M1" s="14">
+        <v>2030</v>
+      </c>
+      <c r="N1" s="14">
+        <v>2031</v>
+      </c>
+      <c r="O1" s="14">
+        <v>2032</v>
+      </c>
+      <c r="P1" s="14">
+        <v>2033</v>
+      </c>
+      <c r="Q1" s="14">
+        <v>2034</v>
+      </c>
+      <c r="R1" s="14">
+        <v>2035</v>
+      </c>
+      <c r="S1" s="14">
+        <v>2036</v>
+      </c>
+      <c r="T1" s="14">
+        <v>2037</v>
+      </c>
+      <c r="U1" s="14">
+        <v>2038</v>
+      </c>
+      <c r="V1" s="14">
+        <v>2039</v>
+      </c>
+      <c r="W1" s="14">
+        <v>2040</v>
+      </c>
+      <c r="X1" s="14">
+        <v>2041</v>
+      </c>
+      <c r="Y1" s="14">
+        <v>2042</v>
+      </c>
+      <c r="Z1" s="14">
+        <v>2043</v>
+      </c>
+      <c r="AA1" s="14">
+        <v>2044</v>
+      </c>
+      <c r="AB1" s="14">
+        <v>2045</v>
+      </c>
+      <c r="AC1" s="14">
+        <v>2046</v>
+      </c>
+      <c r="AD1" s="14">
+        <v>2047</v>
+      </c>
+      <c r="AE1" s="14">
+        <v>2048</v>
+      </c>
+      <c r="AF1" s="14">
+        <v>2049</v>
+      </c>
+      <c r="AG1" s="14">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V2" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X2" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF2" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG2" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U3" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V3" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X3" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE3" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF3" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG3" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X4" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF4" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG4" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V5" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W5" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X5" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD5" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE5" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF5" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG5" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF6" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG6" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE7" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG7" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE8" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF8" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG8" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE9" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF9" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG9" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V10" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG10" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W11" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF11" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG11" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V12" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD12" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE12" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF12" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG12" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V13" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W13" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD13" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE13" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF13" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG13" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD14" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE14" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF14" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG14" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W15" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD15" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE15" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF15" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG15" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S16" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T16" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U16" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V16" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W16" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X16" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD16" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE16" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF16" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG16" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V17" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W17" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD17" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE17" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF17" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG17" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0.95499999999999952</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0.90999999999999959</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.86499999999999955</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0.81999999999999962</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0.77499999999999969</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0.72999999999999965</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0.68499999999999961</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0.63999999999999968</v>
+      </c>
+      <c r="V18" s="2">
+        <v>0.59499999999999975</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0.54999999999999971</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0.50499999999999978</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0.45999999999999974</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>0.41499999999999981</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>0.36999999999999977</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>0.32499999999999984</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>0.27999999999999992</v>
+      </c>
+      <c r="AD18" s="2">
+        <v>0.23499999999999988</v>
+      </c>
+      <c r="AE18" s="2">
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AF18" s="2">
+        <v>0.14499999999999991</v>
+      </c>
+      <c r="AG18" s="2">
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56127C65-188C-4CA3-A752-2C202A8ABC29}">
   <dimension ref="A1:AG20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4690,97 +6518,97 @@
       <c r="B6" s="11">
         <v>0</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="J6" s="30">
+      <c r="J6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="K6" s="30">
+      <c r="K6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="L6" s="30">
+      <c r="L6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="M6" s="30">
+      <c r="M6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="N6" s="30">
+      <c r="N6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="O6" s="30">
+      <c r="O6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="P6" s="30">
+      <c r="P6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="Q6" s="30">
+      <c r="Q6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="R6" s="30">
+      <c r="R6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="S6" s="30">
+      <c r="S6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="T6" s="30">
+      <c r="T6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="U6" s="30">
+      <c r="U6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="V6" s="30">
+      <c r="V6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="W6" s="30">
+      <c r="W6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="X6" s="30">
+      <c r="X6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="Y6" s="30">
+      <c r="Y6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="Z6" s="30">
+      <c r="Z6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AA6" s="30">
+      <c r="AA6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AB6" s="30">
+      <c r="AB6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AC6" s="30">
+      <c r="AC6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AD6" s="30">
+      <c r="AD6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AE6" s="30">
+      <c r="AE6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AF6" s="30">
+      <c r="AF6" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AG6" s="30">
+      <c r="AG6" s="32">
         <v>1E-4</v>
       </c>
     </row>
@@ -4791,97 +6619,97 @@
       <c r="B7" s="12">
         <v>0</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="O7" s="30">
+      <c r="O7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="P7" s="30">
+      <c r="P7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="Q7" s="30">
+      <c r="Q7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="R7" s="30">
+      <c r="R7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="S7" s="30">
+      <c r="S7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="T7" s="30">
+      <c r="T7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="U7" s="30">
+      <c r="U7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="V7" s="30">
+      <c r="V7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="W7" s="30">
+      <c r="W7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="X7" s="30">
+      <c r="X7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="Y7" s="30">
+      <c r="Y7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="Z7" s="30">
+      <c r="Z7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AA7" s="30">
+      <c r="AA7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AB7" s="30">
+      <c r="AB7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AC7" s="30">
+      <c r="AC7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AD7" s="30">
+      <c r="AD7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AE7" s="30">
+      <c r="AE7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AF7" s="30">
+      <c r="AF7" s="32">
         <v>1E-4</v>
       </c>
-      <c r="AG7" s="30">
+      <c r="AG7" s="32">
         <v>1E-4</v>
       </c>
     </row>
@@ -6312,7 +8140,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{249CECFF-F9A5-41C5-BA4B-FC0238B94C34}">
   <dimension ref="A1:AI18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6431,102 +8259,102 @@
       <c r="B2" s="12">
         <v>0</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="27">
         <v>3.3333300000000003E-2</v>
       </c>
-      <c r="D2" s="13">
-        <v>6.6666699999999954E-2</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.11428571428571428</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.12857142857142856</v>
-      </c>
-      <c r="H2" s="13">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="I2" s="13">
-        <v>0.15714285714285714</v>
-      </c>
-      <c r="J2" s="13">
-        <v>0.17142857142857143</v>
-      </c>
-      <c r="K2" s="13">
-        <v>0.18571428571428572</v>
-      </c>
-      <c r="L2" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="M2" s="13">
-        <v>0.21428571428571427</v>
-      </c>
-      <c r="N2" s="13">
-        <v>0.22857142857142856</v>
-      </c>
-      <c r="O2" s="13">
-        <v>0.24285714285714285</v>
-      </c>
-      <c r="P2" s="13">
-        <v>0.25714285714285712</v>
-      </c>
-      <c r="Q2" s="13">
-        <v>0.27142857142857146</v>
-      </c>
-      <c r="R2" s="13">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S2" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="T2" s="13">
-        <v>0.31428571428571428</v>
-      </c>
-      <c r="U2" s="13">
-        <v>0.32857142857142857</v>
-      </c>
-      <c r="V2" s="13">
-        <v>0.34285714285714286</v>
-      </c>
-      <c r="W2" s="13">
-        <v>0.3571428571428571</v>
-      </c>
-      <c r="X2" s="13">
-        <v>0.37142857142857144</v>
-      </c>
-      <c r="Y2" s="13">
-        <v>0.38571428571428568</v>
-      </c>
-      <c r="Z2" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="AA2" s="13">
-        <v>0.41428571428571426</v>
-      </c>
-      <c r="AB2" s="13">
-        <v>0.4285714285714286</v>
-      </c>
-      <c r="AC2" s="13">
-        <v>0.44285714285714284</v>
-      </c>
-      <c r="AD2" s="13">
-        <v>0.45714285714285718</v>
-      </c>
-      <c r="AE2" s="13">
+      <c r="D2" s="27">
+        <v>6.6666699999999995E-2</v>
+      </c>
+      <c r="E2" s="27">
+        <v>9.9999999999999895E-2</v>
+      </c>
+      <c r="F2" s="27">
+        <v>0.12321428571428561</v>
+      </c>
+      <c r="G2" s="27">
+        <v>0.14642857142857135</v>
+      </c>
+      <c r="H2" s="27">
+        <v>0.16964285714285704</v>
+      </c>
+      <c r="I2" s="27">
+        <v>0.19285714285714278</v>
+      </c>
+      <c r="J2" s="27">
+        <v>0.2160714285714285</v>
+      </c>
+      <c r="K2" s="27">
+        <v>0.23928571428571421</v>
+      </c>
+      <c r="L2" s="27">
+        <v>0.26249999999999996</v>
+      </c>
+      <c r="M2" s="27">
+        <v>0.28571428571428564</v>
+      </c>
+      <c r="N2" s="27">
+        <v>0.30892857142857133</v>
+      </c>
+      <c r="O2" s="27">
+        <v>0.33214285714285707</v>
+      </c>
+      <c r="P2" s="27">
+        <v>0.35535714285714282</v>
+      </c>
+      <c r="Q2" s="27">
+        <v>0.3785714285714285</v>
+      </c>
+      <c r="R2" s="27">
+        <v>0.40178571428571425</v>
+      </c>
+      <c r="S2" s="27">
+        <v>0.42499999999999993</v>
+      </c>
+      <c r="T2" s="27">
+        <v>0.44821428571428568</v>
+      </c>
+      <c r="U2" s="27">
         <v>0.47142857142857142</v>
       </c>
-      <c r="AF2" s="13">
-        <v>0.48571428571428565</v>
-      </c>
-      <c r="AG2" s="13">
-        <v>0.5</v>
+      <c r="V2" s="27">
+        <v>0.49464285714285711</v>
+      </c>
+      <c r="W2" s="27">
+        <v>0.51785714285714279</v>
+      </c>
+      <c r="X2" s="27">
+        <v>0.54107142857142854</v>
+      </c>
+      <c r="Y2" s="27">
+        <v>0.56428571428571428</v>
+      </c>
+      <c r="Z2" s="27">
+        <v>0.58749999999999991</v>
+      </c>
+      <c r="AA2" s="27">
+        <v>0.61071428571428577</v>
+      </c>
+      <c r="AB2" s="27">
+        <v>0.6339285714285714</v>
+      </c>
+      <c r="AC2" s="27">
+        <v>0.65714285714285725</v>
+      </c>
+      <c r="AD2" s="27">
+        <v>0.68035714285714288</v>
+      </c>
+      <c r="AE2" s="27">
+        <v>0.70357142857142851</v>
+      </c>
+      <c r="AF2" s="27">
+        <v>0.72678571428571437</v>
+      </c>
+      <c r="AG2" s="27">
+        <v>0.75</v>
       </c>
       <c r="AI2" s="28">
         <f>(AG2-E2)/$AI$1</f>
-        <v>1.4285714285714287E-2</v>
+        <v>2.3214285714285719E-2</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
@@ -6543,122 +8371,95 @@
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="E3" s="27">
-        <v>5.000000000000001E-2</v>
-      </c>
-      <c r="F3" s="13">
-        <f t="shared" ref="F3:F18" si="0">E3+$AI3</f>
-        <v>5.5357142857142869E-2</v>
-      </c>
-      <c r="G3" s="13">
-        <f t="shared" ref="G3:G18" si="1">F3+$AI3</f>
-        <v>6.0714285714285728E-2</v>
-      </c>
-      <c r="H3" s="13">
-        <f t="shared" ref="H3:AE3" si="2">G3+$AI3</f>
-        <v>6.6071428571428586E-2</v>
-      </c>
-      <c r="I3" s="13">
-        <f t="shared" si="2"/>
-        <v>7.1428571428571438E-2</v>
-      </c>
-      <c r="J3" s="13">
-        <f t="shared" si="2"/>
-        <v>7.678571428571429E-2</v>
-      </c>
-      <c r="K3" s="13">
-        <f t="shared" si="2"/>
-        <v>8.2142857142857142E-2</v>
-      </c>
-      <c r="L3" s="13">
-        <f t="shared" si="2"/>
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="M3" s="13">
-        <f t="shared" si="2"/>
-        <v>9.2857142857142846E-2</v>
-      </c>
-      <c r="N3" s="13">
-        <f t="shared" si="2"/>
-        <v>9.8214285714285698E-2</v>
-      </c>
-      <c r="O3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.10357142857142855</v>
-      </c>
-      <c r="P3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.1089285714285714</v>
-      </c>
-      <c r="Q3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.11428571428571425</v>
-      </c>
-      <c r="R3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.11964285714285711</v>
-      </c>
-      <c r="S3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.12499999999999996</v>
-      </c>
-      <c r="T3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.13035714285714281</v>
-      </c>
-      <c r="U3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.13571428571428568</v>
-      </c>
-      <c r="V3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.14107142857142854</v>
-      </c>
-      <c r="W3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.14642857142857141</v>
-      </c>
-      <c r="X3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.15178571428571427</v>
-      </c>
-      <c r="Y3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.15714285714285714</v>
-      </c>
-      <c r="Z3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.16250000000000001</v>
-      </c>
-      <c r="AA3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.16785714285714287</v>
-      </c>
-      <c r="AB3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.17321428571428574</v>
-      </c>
-      <c r="AC3" s="13">
-        <f t="shared" si="2"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="F3" s="27">
+        <v>6.6071428571428614E-2</v>
+      </c>
+      <c r="G3" s="27">
+        <v>8.2142857142857184E-2</v>
+      </c>
+      <c r="H3" s="27">
+        <v>9.8214285714285754E-2</v>
+      </c>
+      <c r="I3" s="27">
+        <v>0.11428571428571432</v>
+      </c>
+      <c r="J3" s="27">
+        <v>0.13035714285714289</v>
+      </c>
+      <c r="K3" s="27">
+        <v>0.14642857142857146</v>
+      </c>
+      <c r="L3" s="27">
+        <v>0.16250000000000003</v>
+      </c>
+      <c r="M3" s="27">
         <v>0.1785714285714286</v>
       </c>
-      <c r="AD3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.18392857142857147</v>
-      </c>
-      <c r="AE3" s="13">
-        <f t="shared" si="2"/>
-        <v>0.18928571428571433</v>
-      </c>
-      <c r="AF3" s="13">
-        <f t="shared" ref="AF3" si="3">AE3+$AI3</f>
-        <v>0.1946428571428572</v>
-      </c>
-      <c r="AG3" s="13">
-        <v>0.2</v>
+      <c r="N3" s="27">
+        <v>0.19464285714285717</v>
+      </c>
+      <c r="O3" s="27">
+        <v>0.21071428571428574</v>
+      </c>
+      <c r="P3" s="27">
+        <v>0.22678571428571431</v>
+      </c>
+      <c r="Q3" s="27">
+        <v>0.24285714285714288</v>
+      </c>
+      <c r="R3" s="27">
+        <v>0.25892857142857145</v>
+      </c>
+      <c r="S3" s="27">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="T3" s="27">
+        <v>0.29107142857142859</v>
+      </c>
+      <c r="U3" s="27">
+        <v>0.30714285714285716</v>
+      </c>
+      <c r="V3" s="27">
+        <v>0.32321428571428573</v>
+      </c>
+      <c r="W3" s="27">
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="X3" s="27">
+        <v>0.35535714285714287</v>
+      </c>
+      <c r="Y3" s="27">
+        <v>0.37142857142857144</v>
+      </c>
+      <c r="Z3" s="27">
+        <v>0.38750000000000001</v>
+      </c>
+      <c r="AA3" s="27">
+        <v>0.40357142857142858</v>
+      </c>
+      <c r="AB3" s="27">
+        <v>0.41964285714285715</v>
+      </c>
+      <c r="AC3" s="27">
+        <v>0.43571428571428572</v>
+      </c>
+      <c r="AD3" s="27">
+        <v>0.45178571428571429</v>
+      </c>
+      <c r="AE3" s="27">
+        <v>0.46785714285714286</v>
+      </c>
+      <c r="AF3" s="27">
+        <v>0.48392857142857143</v>
+      </c>
+      <c r="AG3" s="27">
+        <v>0.5</v>
       </c>
       <c r="AI3" s="28">
-        <f t="shared" ref="AI3:AI18" si="4">(AG3-E3)/$AI$1</f>
-        <v>5.3571428571428572E-3</v>
+        <f t="shared" ref="AI3:AI18" si="0">(AG3-E3)/$AI$1</f>
+        <v>1.607142857142857E-2</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.3">
@@ -6668,129 +8469,102 @@
       <c r="B4" s="12">
         <v>0</v>
       </c>
-      <c r="C4" s="13">
-        <v>3.3333333333333326E-2</v>
-      </c>
-      <c r="D4" s="13">
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="E4" s="13">
-        <v>0.10000000000000002</v>
-      </c>
-      <c r="F4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.11071428571428574</v>
-      </c>
-      <c r="G4" s="13">
-        <f t="shared" si="1"/>
-        <v>0.12142857142857146</v>
-      </c>
-      <c r="H4" s="13">
-        <f t="shared" ref="H4:AE4" si="5">G4+$AI4</f>
-        <v>0.13214285714285717</v>
-      </c>
-      <c r="I4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.14285714285714288</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.15357142857142858</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.16428571428571428</v>
-      </c>
-      <c r="L4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="M4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.18571428571428569</v>
-      </c>
-      <c r="N4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.1964285714285714</v>
-      </c>
-      <c r="O4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.2071428571428571</v>
-      </c>
-      <c r="P4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.2178571428571428</v>
-      </c>
-      <c r="Q4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.22857142857142851</v>
-      </c>
-      <c r="R4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.23928571428571421</v>
-      </c>
-      <c r="S4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.24999999999999992</v>
-      </c>
-      <c r="T4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.26071428571428562</v>
-      </c>
-      <c r="U4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.27142857142857135</v>
-      </c>
-      <c r="V4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.28214285714285708</v>
-      </c>
-      <c r="W4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.29285714285714282</v>
-      </c>
-      <c r="X4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.30357142857142855</v>
-      </c>
-      <c r="Y4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.31428571428571428</v>
-      </c>
-      <c r="Z4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="AA4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.33571428571428574</v>
-      </c>
-      <c r="AB4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.34642857142857147</v>
-      </c>
-      <c r="AC4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.35714285714285721</v>
-      </c>
-      <c r="AD4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.36785714285714294</v>
-      </c>
-      <c r="AE4" s="13">
-        <f t="shared" si="5"/>
-        <v>0.37857142857142867</v>
-      </c>
-      <c r="AF4" s="13">
-        <f t="shared" ref="AF4" si="6">AE4+$AI4</f>
-        <v>0.3892857142857144</v>
-      </c>
-      <c r="AG4" s="13">
-        <v>0.4</v>
+      <c r="C4" s="27">
+        <v>3.3333300000000003E-2</v>
+      </c>
+      <c r="D4" s="27">
+        <v>6.6666699999999995E-2</v>
+      </c>
+      <c r="E4" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="27">
+        <v>0.18571399999999999</v>
+      </c>
+      <c r="G4" s="27">
+        <v>0.27142899999999998</v>
+      </c>
+      <c r="H4" s="27">
+        <v>0.35714299999999999</v>
+      </c>
+      <c r="I4" s="27">
+        <v>0.442857</v>
+      </c>
+      <c r="J4" s="27">
+        <v>0.52857100000000001</v>
+      </c>
+      <c r="K4" s="27">
+        <v>0.614286</v>
+      </c>
+      <c r="L4" s="27">
+        <v>0.7</v>
+      </c>
+      <c r="M4" s="27">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="N4" s="27">
+        <v>0.83142857142857141</v>
+      </c>
+      <c r="O4" s="27">
+        <v>0.87714285714285711</v>
+      </c>
+      <c r="P4" s="27">
+        <v>0.92285714285714282</v>
+      </c>
+      <c r="Q4" s="27">
+        <v>0.96857142857142853</v>
+      </c>
+      <c r="R4" s="27">
+        <v>1.0142857142857142</v>
+      </c>
+      <c r="S4" s="27">
+        <v>1.06</v>
+      </c>
+      <c r="T4" s="27">
+        <v>1.1057142857142856</v>
+      </c>
+      <c r="U4" s="27">
+        <v>1.1514285714285715</v>
+      </c>
+      <c r="V4" s="27">
+        <v>1.1971428571428571</v>
+      </c>
+      <c r="W4" s="27">
+        <v>1.2428571428571429</v>
+      </c>
+      <c r="X4" s="27">
+        <v>1.2885714285714287</v>
+      </c>
+      <c r="Y4" s="27">
+        <v>1.3342857142857143</v>
+      </c>
+      <c r="Z4" s="27">
+        <v>1.38</v>
+      </c>
+      <c r="AA4" s="27">
+        <v>1.4257142857142857</v>
+      </c>
+      <c r="AB4" s="27">
+        <v>1.4714285714285715</v>
+      </c>
+      <c r="AC4" s="27">
+        <v>1.5171428571428571</v>
+      </c>
+      <c r="AD4" s="27">
+        <v>1.5628571428571427</v>
+      </c>
+      <c r="AE4" s="27">
+        <v>1.6085714285714285</v>
+      </c>
+      <c r="AF4" s="27">
+        <v>1.6542857142857144</v>
+      </c>
+      <c r="AG4" s="27">
+        <v>1.7</v>
       </c>
       <c r="AI4" s="28">
-        <f t="shared" si="4"/>
-        <v>1.0714285714285714E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.7142857142857141E-2</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.3">
@@ -6801,396 +8575,365 @@
         <v>0</v>
       </c>
       <c r="C5" s="27">
-        <v>0.01</v>
+        <v>1.6666666666666663E-2</v>
       </c>
       <c r="D5" s="27">
-        <v>0.01</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="E5" s="27">
-        <v>0.01</v>
+        <v>5.000000000000001E-2</v>
       </c>
       <c r="F5" s="13">
-        <f t="shared" si="0"/>
-        <v>1.3214285714285715E-2</v>
+        <f t="shared" ref="F5" si="1">E5+$AI5</f>
+        <v>5.5357142857142869E-2</v>
       </c>
       <c r="G5" s="13">
-        <f t="shared" si="1"/>
-        <v>1.6428571428571431E-2</v>
+        <f t="shared" ref="G5" si="2">F5+$AI5</f>
+        <v>6.0714285714285728E-2</v>
       </c>
       <c r="H5" s="13">
-        <f t="shared" ref="H5:AE6" si="7">G5+$AI5</f>
-        <v>1.9642857142857146E-2</v>
+        <f t="shared" ref="H5" si="3">G5+$AI5</f>
+        <v>6.6071428571428586E-2</v>
       </c>
       <c r="I5" s="13">
-        <f t="shared" si="7"/>
-        <v>2.2857142857142861E-2</v>
+        <f t="shared" ref="I5" si="4">H5+$AI5</f>
+        <v>7.1428571428571438E-2</v>
       </c>
       <c r="J5" s="13">
-        <f t="shared" si="7"/>
-        <v>2.6071428571428575E-2</v>
+        <f t="shared" ref="J5" si="5">I5+$AI5</f>
+        <v>7.678571428571429E-2</v>
       </c>
       <c r="K5" s="13">
-        <f t="shared" si="7"/>
-        <v>2.928571428571429E-2</v>
+        <f t="shared" ref="K5" si="6">J5+$AI5</f>
+        <v>8.2142857142857142E-2</v>
       </c>
       <c r="L5" s="13">
-        <f t="shared" si="7"/>
-        <v>3.2500000000000001E-2</v>
+        <f t="shared" ref="L5" si="7">K5+$AI5</f>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="M5" s="13">
-        <f t="shared" si="7"/>
-        <v>3.5714285714285712E-2</v>
+        <f t="shared" ref="M5" si="8">L5+$AI5</f>
+        <v>9.2857142857142846E-2</v>
       </c>
       <c r="N5" s="13">
-        <f t="shared" si="7"/>
-        <v>3.8928571428571423E-2</v>
+        <f t="shared" ref="N5" si="9">M5+$AI5</f>
+        <v>9.8214285714285698E-2</v>
       </c>
       <c r="O5" s="13">
-        <f t="shared" si="7"/>
-        <v>4.2142857142857135E-2</v>
+        <f t="shared" ref="O5" si="10">N5+$AI5</f>
+        <v>0.10357142857142855</v>
       </c>
       <c r="P5" s="13">
-        <f t="shared" si="7"/>
-        <v>4.5357142857142846E-2</v>
+        <f t="shared" ref="P5" si="11">O5+$AI5</f>
+        <v>0.1089285714285714</v>
       </c>
       <c r="Q5" s="13">
-        <f t="shared" si="7"/>
-        <v>4.8571428571428557E-2</v>
+        <f t="shared" ref="Q5" si="12">P5+$AI5</f>
+        <v>0.11428571428571425</v>
       </c>
       <c r="R5" s="13">
-        <f t="shared" si="7"/>
-        <v>5.1785714285714268E-2</v>
+        <f t="shared" ref="R5" si="13">Q5+$AI5</f>
+        <v>0.11964285714285711</v>
       </c>
       <c r="S5" s="13">
-        <f t="shared" si="7"/>
-        <v>5.4999999999999979E-2</v>
+        <f t="shared" ref="S5" si="14">R5+$AI5</f>
+        <v>0.12499999999999996</v>
       </c>
       <c r="T5" s="13">
-        <f t="shared" si="7"/>
-        <v>5.8214285714285691E-2</v>
+        <f t="shared" ref="T5" si="15">S5+$AI5</f>
+        <v>0.13035714285714281</v>
       </c>
       <c r="U5" s="13">
-        <f t="shared" si="7"/>
-        <v>6.1428571428571402E-2</v>
+        <f t="shared" ref="U5" si="16">T5+$AI5</f>
+        <v>0.13571428571428568</v>
       </c>
       <c r="V5" s="13">
-        <f t="shared" si="7"/>
-        <v>6.4642857142857113E-2</v>
+        <f t="shared" ref="V5" si="17">U5+$AI5</f>
+        <v>0.14107142857142854</v>
       </c>
       <c r="W5" s="13">
-        <f t="shared" si="7"/>
-        <v>6.7857142857142824E-2</v>
+        <f t="shared" ref="W5" si="18">V5+$AI5</f>
+        <v>0.14642857142857141</v>
       </c>
       <c r="X5" s="13">
-        <f t="shared" si="7"/>
-        <v>7.1071428571428535E-2</v>
+        <f t="shared" ref="X5" si="19">W5+$AI5</f>
+        <v>0.15178571428571427</v>
       </c>
       <c r="Y5" s="13">
-        <f t="shared" si="7"/>
-        <v>7.4285714285714247E-2</v>
+        <f t="shared" ref="Y5" si="20">X5+$AI5</f>
+        <v>0.15714285714285714</v>
       </c>
       <c r="Z5" s="13">
-        <f t="shared" si="7"/>
-        <v>7.7499999999999958E-2</v>
+        <f t="shared" ref="Z5" si="21">Y5+$AI5</f>
+        <v>0.16250000000000001</v>
       </c>
       <c r="AA5" s="13">
-        <f t="shared" si="7"/>
-        <v>8.0714285714285669E-2</v>
+        <f t="shared" ref="AA5" si="22">Z5+$AI5</f>
+        <v>0.16785714285714287</v>
       </c>
       <c r="AB5" s="13">
-        <f t="shared" si="7"/>
-        <v>8.392857142857138E-2</v>
+        <f t="shared" ref="AB5" si="23">AA5+$AI5</f>
+        <v>0.17321428571428574</v>
       </c>
       <c r="AC5" s="13">
-        <f t="shared" si="7"/>
-        <v>8.7142857142857091E-2</v>
+        <f t="shared" ref="AC5" si="24">AB5+$AI5</f>
+        <v>0.1785714285714286</v>
       </c>
       <c r="AD5" s="13">
-        <f t="shared" si="7"/>
-        <v>9.0357142857142803E-2</v>
+        <f t="shared" ref="AD5" si="25">AC5+$AI5</f>
+        <v>0.18392857142857147</v>
       </c>
       <c r="AE5" s="13">
-        <f t="shared" si="7"/>
-        <v>9.3571428571428514E-2</v>
+        <f t="shared" ref="AE5" si="26">AD5+$AI5</f>
+        <v>0.18928571428571433</v>
       </c>
       <c r="AF5" s="13">
-        <f t="shared" ref="AF5:AF6" si="8">AE5+$AI5</f>
-        <v>9.6785714285714225E-2</v>
+        <f t="shared" ref="AF5" si="27">AE5+$AI5</f>
+        <v>0.1946428571428572</v>
       </c>
       <c r="AG5" s="13">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AI5" s="28">
-        <f t="shared" si="4"/>
-        <v>3.2142857142857147E-3</v>
+        <f t="shared" si="0"/>
+        <v>5.3571428571428572E-3</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="31">
         <v>0</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="35">
         <v>1E-4</v>
       </c>
-      <c r="D6" s="31">
-        <f>C6</f>
+      <c r="D6" s="35">
         <v>1E-4</v>
       </c>
-      <c r="E6" s="31">
-        <f>D6</f>
+      <c r="E6" s="35">
         <v>1E-4</v>
       </c>
-      <c r="F6" s="32">
-        <f t="shared" ref="F6" si="9">E6+$AI6</f>
-        <v>1.3214285714285715E-4</v>
-      </c>
-      <c r="G6" s="32">
-        <f t="shared" ref="G6" si="10">F6+$AI6</f>
-        <v>1.6428571428571431E-4</v>
-      </c>
-      <c r="H6" s="32">
-        <f t="shared" si="7"/>
-        <v>1.9642857142857146E-4</v>
-      </c>
-      <c r="I6" s="32">
-        <f t="shared" si="7"/>
-        <v>2.2857142857142862E-4</v>
-      </c>
-      <c r="J6" s="32">
-        <f t="shared" si="7"/>
-        <v>2.6071428571428578E-4</v>
-      </c>
-      <c r="K6" s="32">
-        <f t="shared" si="7"/>
-        <v>2.9285714285714294E-4</v>
-      </c>
-      <c r="L6" s="32">
-        <f t="shared" si="7"/>
-        <v>3.2500000000000009E-4</v>
-      </c>
-      <c r="M6" s="32">
-        <f t="shared" si="7"/>
-        <v>3.5714285714285725E-4</v>
-      </c>
-      <c r="N6" s="32">
-        <f t="shared" si="7"/>
-        <v>3.8928571428571441E-4</v>
-      </c>
-      <c r="O6" s="32">
-        <f t="shared" si="7"/>
-        <v>4.2142857142857157E-4</v>
-      </c>
-      <c r="P6" s="32">
-        <f t="shared" si="7"/>
-        <v>4.5357142857142872E-4</v>
-      </c>
-      <c r="Q6" s="32">
-        <f t="shared" si="7"/>
-        <v>4.8571428571428588E-4</v>
-      </c>
-      <c r="R6" s="32">
-        <f t="shared" si="7"/>
-        <v>5.1785714285714304E-4</v>
-      </c>
-      <c r="S6" s="32">
-        <f t="shared" si="7"/>
-        <v>5.5000000000000014E-4</v>
-      </c>
-      <c r="T6" s="32">
-        <f t="shared" si="7"/>
-        <v>5.8214285714285724E-4</v>
-      </c>
-      <c r="U6" s="32">
-        <f t="shared" si="7"/>
-        <v>6.1428571428571435E-4</v>
-      </c>
-      <c r="V6" s="32">
-        <f t="shared" si="7"/>
-        <v>6.4642857142857145E-4</v>
-      </c>
-      <c r="W6" s="32">
-        <f t="shared" si="7"/>
-        <v>6.7857142857142855E-4</v>
-      </c>
-      <c r="X6" s="32">
-        <f t="shared" si="7"/>
-        <v>7.1071428571428566E-4</v>
-      </c>
-      <c r="Y6" s="32">
-        <f t="shared" si="7"/>
-        <v>7.4285714285714276E-4</v>
-      </c>
-      <c r="Z6" s="32">
-        <f t="shared" si="7"/>
-        <v>7.7499999999999986E-4</v>
-      </c>
-      <c r="AA6" s="32">
-        <f t="shared" si="7"/>
-        <v>8.0714285714285697E-4</v>
-      </c>
-      <c r="AB6" s="32">
-        <f t="shared" si="7"/>
-        <v>8.3928571428571407E-4</v>
-      </c>
-      <c r="AC6" s="32">
-        <f t="shared" si="7"/>
-        <v>8.7142857142857117E-4</v>
-      </c>
-      <c r="AD6" s="32">
-        <f t="shared" si="7"/>
-        <v>9.0357142857142828E-4</v>
-      </c>
-      <c r="AE6" s="32">
-        <f t="shared" si="7"/>
-        <v>9.3571428571428538E-4</v>
-      </c>
-      <c r="AF6" s="32">
-        <f t="shared" si="8"/>
-        <v>9.6785714285714248E-4</v>
-      </c>
-      <c r="AG6" s="32">
-        <v>1E-3</v>
+      <c r="F6" s="35">
+        <v>8.107142857142844E-4</v>
+      </c>
+      <c r="G6" s="35">
+        <v>1.5214285714285703E-3</v>
+      </c>
+      <c r="H6" s="35">
+        <v>2.2321428571428562E-3</v>
+      </c>
+      <c r="I6" s="35">
+        <v>2.942857142857142E-3</v>
+      </c>
+      <c r="J6" s="35">
+        <v>3.6535714285714279E-3</v>
+      </c>
+      <c r="K6" s="35">
+        <v>4.3642857142857138E-3</v>
+      </c>
+      <c r="L6" s="35">
+        <v>5.0749999999999997E-3</v>
+      </c>
+      <c r="M6" s="35">
+        <v>5.7857142857142855E-3</v>
+      </c>
+      <c r="N6" s="35">
+        <v>6.4964285714285714E-3</v>
+      </c>
+      <c r="O6" s="35">
+        <v>7.2071428571428564E-3</v>
+      </c>
+      <c r="P6" s="35">
+        <v>7.9178571428571431E-3</v>
+      </c>
+      <c r="Q6" s="35">
+        <v>8.6285714285714299E-3</v>
+      </c>
+      <c r="R6" s="35">
+        <v>9.3392857142857149E-3</v>
+      </c>
+      <c r="S6" s="35">
+        <v>1.005E-2</v>
+      </c>
+      <c r="T6" s="35">
+        <v>1.0760714285714287E-2</v>
+      </c>
+      <c r="U6" s="35">
+        <v>1.1471428571428573E-2</v>
+      </c>
+      <c r="V6" s="35">
+        <v>1.2182142857142858E-2</v>
+      </c>
+      <c r="W6" s="35">
+        <v>1.2892857142857143E-2</v>
+      </c>
+      <c r="X6" s="35">
+        <v>1.360357142857143E-2</v>
+      </c>
+      <c r="Y6" s="35">
+        <v>1.4314285714285717E-2</v>
+      </c>
+      <c r="Z6" s="35">
+        <v>1.5025E-2</v>
+      </c>
+      <c r="AA6" s="35">
+        <v>1.5735714285714287E-2</v>
+      </c>
+      <c r="AB6" s="35">
+        <v>1.6446428571428574E-2</v>
+      </c>
+      <c r="AC6" s="35">
+        <v>1.715714285714286E-2</v>
+      </c>
+      <c r="AD6" s="35">
+        <v>1.7867857142857147E-2</v>
+      </c>
+      <c r="AE6" s="35">
+        <v>1.857857142857143E-2</v>
+      </c>
+      <c r="AF6" s="35">
+        <v>1.9289285714285717E-2</v>
+      </c>
+      <c r="AG6" s="35">
+        <v>2.0000000000000004E-2</v>
       </c>
       <c r="AI6" s="28">
-        <f t="shared" si="4"/>
-        <v>3.2142857142857144E-5</v>
+        <f t="shared" si="0"/>
+        <v>7.1071428571428587E-4</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="34">
         <v>0</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="35">
         <v>1E-4</v>
       </c>
-      <c r="D7" s="31">
-        <f>C7</f>
+      <c r="D7" s="35">
         <v>1E-4</v>
       </c>
-      <c r="E7" s="31">
-        <f>D7</f>
+      <c r="E7" s="35">
         <v>1E-4</v>
       </c>
-      <c r="F7" s="32">
-        <f t="shared" si="0"/>
-        <v>1.3214285714285715E-4</v>
-      </c>
-      <c r="G7" s="32">
-        <f t="shared" si="1"/>
-        <v>1.6428571428571431E-4</v>
-      </c>
-      <c r="H7" s="32">
-        <f t="shared" ref="H7:AE7" si="11">G7+$AI7</f>
-        <v>1.9642857142857146E-4</v>
-      </c>
-      <c r="I7" s="32">
-        <f t="shared" si="11"/>
-        <v>2.2857142857142862E-4</v>
-      </c>
-      <c r="J7" s="32">
-        <f t="shared" si="11"/>
-        <v>2.6071428571428578E-4</v>
-      </c>
-      <c r="K7" s="32">
-        <f t="shared" si="11"/>
-        <v>2.9285714285714294E-4</v>
-      </c>
-      <c r="L7" s="32">
-        <f t="shared" si="11"/>
-        <v>3.2500000000000009E-4</v>
-      </c>
-      <c r="M7" s="32">
-        <f t="shared" si="11"/>
-        <v>3.5714285714285725E-4</v>
-      </c>
-      <c r="N7" s="32">
-        <f t="shared" si="11"/>
-        <v>3.8928571428571441E-4</v>
-      </c>
-      <c r="O7" s="32">
-        <f t="shared" si="11"/>
-        <v>4.2142857142857157E-4</v>
-      </c>
-      <c r="P7" s="32">
-        <f t="shared" si="11"/>
-        <v>4.5357142857142872E-4</v>
-      </c>
-      <c r="Q7" s="32">
-        <f t="shared" si="11"/>
-        <v>4.8571428571428588E-4</v>
-      </c>
-      <c r="R7" s="32">
-        <f t="shared" si="11"/>
-        <v>5.1785714285714304E-4</v>
-      </c>
-      <c r="S7" s="32">
-        <f t="shared" si="11"/>
-        <v>5.5000000000000014E-4</v>
-      </c>
-      <c r="T7" s="32">
-        <f t="shared" si="11"/>
-        <v>5.8214285714285724E-4</v>
-      </c>
-      <c r="U7" s="32">
-        <f t="shared" si="11"/>
-        <v>6.1428571428571435E-4</v>
-      </c>
-      <c r="V7" s="32">
-        <f t="shared" si="11"/>
-        <v>6.4642857142857145E-4</v>
-      </c>
-      <c r="W7" s="32">
-        <f t="shared" si="11"/>
-        <v>6.7857142857142855E-4</v>
-      </c>
-      <c r="X7" s="32">
-        <f t="shared" si="11"/>
-        <v>7.1071428571428566E-4</v>
-      </c>
-      <c r="Y7" s="32">
-        <f t="shared" si="11"/>
-        <v>7.4285714285714276E-4</v>
-      </c>
-      <c r="Z7" s="32">
-        <f t="shared" si="11"/>
-        <v>7.7499999999999986E-4</v>
-      </c>
-      <c r="AA7" s="32">
-        <f t="shared" si="11"/>
-        <v>8.0714285714285697E-4</v>
-      </c>
-      <c r="AB7" s="32">
-        <f t="shared" si="11"/>
-        <v>8.3928571428571407E-4</v>
-      </c>
-      <c r="AC7" s="32">
-        <f t="shared" si="11"/>
-        <v>8.7142857142857117E-4</v>
-      </c>
-      <c r="AD7" s="32">
-        <f t="shared" si="11"/>
-        <v>9.0357142857142828E-4</v>
-      </c>
-      <c r="AE7" s="32">
-        <f t="shared" si="11"/>
-        <v>9.3571428571428538E-4</v>
-      </c>
-      <c r="AF7" s="32">
-        <f t="shared" ref="AF7" si="12">AE7+$AI7</f>
-        <v>9.6785714285714248E-4</v>
-      </c>
-      <c r="AG7" s="32">
-        <v>1E-3</v>
+      <c r="F7" s="36">
+        <f t="shared" ref="F6:G18" si="28">E7+$AI7</f>
+        <v>1.8821428571428572E-3</v>
+      </c>
+      <c r="G7" s="36">
+        <f t="shared" si="28"/>
+        <v>3.6642857142857145E-3</v>
+      </c>
+      <c r="H7" s="36">
+        <f t="shared" ref="G6:V18" si="29">G7+$AI7</f>
+        <v>5.4464285714285717E-3</v>
+      </c>
+      <c r="I7" s="36">
+        <f t="shared" si="29"/>
+        <v>7.2285714285714288E-3</v>
+      </c>
+      <c r="J7" s="36">
+        <f t="shared" si="29"/>
+        <v>9.0107142857142851E-3</v>
+      </c>
+      <c r="K7" s="36">
+        <f t="shared" si="29"/>
+        <v>1.0792857142857142E-2</v>
+      </c>
+      <c r="L7" s="36">
+        <f t="shared" si="29"/>
+        <v>1.2574999999999999E-2</v>
+      </c>
+      <c r="M7" s="36">
+        <f t="shared" si="29"/>
+        <v>1.4357142857142857E-2</v>
+      </c>
+      <c r="N7" s="36">
+        <f t="shared" si="29"/>
+        <v>1.6139285714285714E-2</v>
+      </c>
+      <c r="O7" s="36">
+        <f t="shared" si="29"/>
+        <v>1.7921428571428571E-2</v>
+      </c>
+      <c r="P7" s="36">
+        <f t="shared" si="29"/>
+        <v>1.9703571428571428E-2</v>
+      </c>
+      <c r="Q7" s="36">
+        <f t="shared" si="29"/>
+        <v>2.1485714285714285E-2</v>
+      </c>
+      <c r="R7" s="36">
+        <f t="shared" si="29"/>
+        <v>2.3267857142857142E-2</v>
+      </c>
+      <c r="S7" s="36">
+        <f t="shared" si="29"/>
+        <v>2.5049999999999999E-2</v>
+      </c>
+      <c r="T7" s="36">
+        <f t="shared" si="29"/>
+        <v>2.6832142857142856E-2</v>
+      </c>
+      <c r="U7" s="36">
+        <f t="shared" si="29"/>
+        <v>2.8614285714285714E-2</v>
+      </c>
+      <c r="V7" s="36">
+        <f t="shared" si="29"/>
+        <v>3.0396428571428571E-2</v>
+      </c>
+      <c r="W7" s="36">
+        <f t="shared" ref="W6:AE7" si="30">V7+$AI7</f>
+        <v>3.2178571428571431E-2</v>
+      </c>
+      <c r="X7" s="36">
+        <f t="shared" si="30"/>
+        <v>3.3960714285714289E-2</v>
+      </c>
+      <c r="Y7" s="36">
+        <f t="shared" si="30"/>
+        <v>3.5742857142857146E-2</v>
+      </c>
+      <c r="Z7" s="36">
+        <f t="shared" si="30"/>
+        <v>3.7525000000000003E-2</v>
+      </c>
+      <c r="AA7" s="36">
+        <f t="shared" si="30"/>
+        <v>3.930714285714286E-2</v>
+      </c>
+      <c r="AB7" s="36">
+        <f t="shared" si="30"/>
+        <v>4.1089285714285717E-2</v>
+      </c>
+      <c r="AC7" s="36">
+        <f t="shared" si="30"/>
+        <v>4.2871428571428574E-2</v>
+      </c>
+      <c r="AD7" s="36">
+        <f t="shared" si="30"/>
+        <v>4.4653571428571431E-2</v>
+      </c>
+      <c r="AE7" s="36">
+        <f t="shared" si="30"/>
+        <v>4.6435714285714288E-2</v>
+      </c>
+      <c r="AF7" s="36">
+        <f t="shared" ref="AF6:AF7" si="31">AE7+$AI7</f>
+        <v>4.8217857142857146E-2</v>
+      </c>
+      <c r="AG7" s="36">
+        <v>0.05</v>
       </c>
       <c r="AI7" s="28">
-        <f t="shared" si="4"/>
-        <v>3.2142857142857144E-5</v>
+        <f t="shared" si="0"/>
+        <v>1.7821428571428571E-3</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.3">
@@ -7210,118 +8953,118 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="F8" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="28"/>
         <v>0.22142857142857147</v>
       </c>
       <c r="G8" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="29"/>
         <v>0.24285714285714291</v>
       </c>
       <c r="H8" s="13">
-        <f t="shared" ref="H8:AE8" si="13">G8+$AI8</f>
+        <f t="shared" ref="H8:AE8" si="32">G8+$AI8</f>
         <v>0.26428571428571435</v>
       </c>
       <c r="I8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.28571428571428575</v>
       </c>
       <c r="J8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.30714285714285716</v>
       </c>
       <c r="K8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.32857142857142857</v>
       </c>
       <c r="L8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
       <c r="M8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.37142857142857139</v>
       </c>
       <c r="N8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.39285714285714279</v>
       </c>
       <c r="O8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.4142857142857142</v>
       </c>
       <c r="P8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.43571428571428561</v>
       </c>
       <c r="Q8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.45714285714285702</v>
       </c>
       <c r="R8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.47857142857142843</v>
       </c>
       <c r="S8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.49999999999999983</v>
       </c>
       <c r="T8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.52142857142857124</v>
       </c>
       <c r="U8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.5428571428571427</v>
       </c>
       <c r="V8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.56428571428571417</v>
       </c>
       <c r="W8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.58571428571428563</v>
       </c>
       <c r="X8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.6071428571428571</v>
       </c>
       <c r="Y8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.62857142857142856</v>
       </c>
       <c r="Z8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.65</v>
       </c>
       <c r="AA8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.67142857142857149</v>
       </c>
       <c r="AB8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.69285714285714295</v>
       </c>
       <c r="AC8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.71428571428571441</v>
       </c>
       <c r="AD8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.73571428571428588</v>
       </c>
       <c r="AE8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="32"/>
         <v>0.75714285714285734</v>
       </c>
       <c r="AF8" s="13">
-        <f t="shared" ref="AF8" si="14">AE8+$AI8</f>
+        <f t="shared" ref="AF8" si="33">AE8+$AI8</f>
         <v>0.7785714285714288</v>
       </c>
       <c r="AG8" s="13">
         <v>0.8</v>
       </c>
       <c r="AI8" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>2.1428571428571429E-2</v>
       </c>
     </row>
@@ -7342,118 +9085,118 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="F9" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="28"/>
         <v>5.5357142857142869E-2</v>
       </c>
       <c r="G9" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="29"/>
         <v>6.0714285714285728E-2</v>
       </c>
       <c r="H9" s="13">
-        <f t="shared" ref="H9:AE9" si="15">G9+$AI9</f>
+        <f t="shared" ref="H9:AE9" si="34">G9+$AI9</f>
         <v>6.6071428571428586E-2</v>
       </c>
       <c r="I9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>7.1428571428571438E-2</v>
       </c>
       <c r="J9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>7.678571428571429E-2</v>
       </c>
       <c r="K9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>8.2142857142857142E-2</v>
       </c>
       <c r="L9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>8.7499999999999994E-2</v>
       </c>
       <c r="M9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>9.2857142857142846E-2</v>
       </c>
       <c r="N9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>9.8214285714285698E-2</v>
       </c>
       <c r="O9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.10357142857142855</v>
       </c>
       <c r="P9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.1089285714285714</v>
       </c>
       <c r="Q9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.11428571428571425</v>
       </c>
       <c r="R9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.11964285714285711</v>
       </c>
       <c r="S9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.12499999999999996</v>
       </c>
       <c r="T9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.13035714285714281</v>
       </c>
       <c r="U9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.13571428571428568</v>
       </c>
       <c r="V9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.14107142857142854</v>
       </c>
       <c r="W9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.14642857142857141</v>
       </c>
       <c r="X9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.15178571428571427</v>
       </c>
       <c r="Y9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.15714285714285714</v>
       </c>
       <c r="Z9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.16250000000000001</v>
       </c>
       <c r="AA9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.16785714285714287</v>
       </c>
       <c r="AB9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.17321428571428574</v>
       </c>
       <c r="AC9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.1785714285714286</v>
       </c>
       <c r="AD9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.18392857142857147</v>
       </c>
       <c r="AE9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="34"/>
         <v>0.18928571428571433</v>
       </c>
       <c r="AF9" s="13">
-        <f t="shared" ref="AF9" si="16">AE9+$AI9</f>
+        <f t="shared" ref="AF9" si="35">AE9+$AI9</f>
         <v>0.1946428571428572</v>
       </c>
       <c r="AG9" s="13">
         <v>0.2</v>
       </c>
       <c r="AI9" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>5.3571428571428572E-3</v>
       </c>
     </row>
@@ -7474,118 +9217,118 @@
         <v>0.40000000000000008</v>
       </c>
       <c r="F10" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="28"/>
         <v>0.44285714285714295</v>
       </c>
       <c r="G10" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="29"/>
         <v>0.48571428571428582</v>
       </c>
       <c r="H10" s="13">
-        <f t="shared" ref="H10:AE10" si="17">G10+$AI10</f>
+        <f t="shared" ref="H10:AE10" si="36">G10+$AI10</f>
         <v>0.52857142857142869</v>
       </c>
       <c r="I10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>0.57142857142857151</v>
       </c>
       <c r="J10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>0.61428571428571432</v>
       </c>
       <c r="K10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>0.65714285714285714</v>
       </c>
       <c r="L10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>0.7</v>
       </c>
       <c r="M10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>0.74285714285714277</v>
       </c>
       <c r="N10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>0.78571428571428559</v>
       </c>
       <c r="O10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>0.8285714285714284</v>
       </c>
       <c r="P10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>0.87142857142857122</v>
       </c>
       <c r="Q10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>0.91428571428571404</v>
       </c>
       <c r="R10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>0.95714285714285685</v>
       </c>
       <c r="S10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>0.99999999999999967</v>
       </c>
       <c r="T10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.0428571428571425</v>
       </c>
       <c r="U10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.0857142857142854</v>
       </c>
       <c r="V10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.1285714285714283</v>
       </c>
       <c r="W10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.1714285714285713</v>
       </c>
       <c r="X10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="Y10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.2571428571428571</v>
       </c>
       <c r="Z10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.3</v>
       </c>
       <c r="AA10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.342857142857143</v>
       </c>
       <c r="AB10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.3857142857142859</v>
       </c>
       <c r="AC10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.4285714285714288</v>
       </c>
       <c r="AD10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.4714285714285718</v>
       </c>
       <c r="AE10" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>1.5142857142857147</v>
       </c>
       <c r="AF10" s="13">
-        <f t="shared" ref="AF10" si="18">AE10+$AI10</f>
+        <f t="shared" ref="AF10" si="37">AE10+$AI10</f>
         <v>1.5571428571428576</v>
       </c>
       <c r="AG10" s="13">
         <v>1.6</v>
       </c>
       <c r="AI10" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>4.2857142857142858E-2</v>
       </c>
     </row>
@@ -7606,118 +9349,118 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="F11" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="28"/>
         <v>5.5357142857142869E-2</v>
       </c>
       <c r="G11" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="29"/>
         <v>6.0714285714285728E-2</v>
       </c>
       <c r="H11" s="13">
-        <f t="shared" ref="H11:AE11" si="19">G11+$AI11</f>
+        <f t="shared" ref="H11:AE11" si="38">G11+$AI11</f>
         <v>6.6071428571428586E-2</v>
       </c>
       <c r="I11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>7.1428571428571438E-2</v>
       </c>
       <c r="J11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>7.678571428571429E-2</v>
       </c>
       <c r="K11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>8.2142857142857142E-2</v>
       </c>
       <c r="L11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>8.7499999999999994E-2</v>
       </c>
       <c r="M11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>9.2857142857142846E-2</v>
       </c>
       <c r="N11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>9.8214285714285698E-2</v>
       </c>
       <c r="O11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.10357142857142855</v>
       </c>
       <c r="P11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.1089285714285714</v>
       </c>
       <c r="Q11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.11428571428571425</v>
       </c>
       <c r="R11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.11964285714285711</v>
       </c>
       <c r="S11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.12499999999999996</v>
       </c>
       <c r="T11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.13035714285714281</v>
       </c>
       <c r="U11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.13571428571428568</v>
       </c>
       <c r="V11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.14107142857142854</v>
       </c>
       <c r="W11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.14642857142857141</v>
       </c>
       <c r="X11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.15178571428571427</v>
       </c>
       <c r="Y11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.15714285714285714</v>
       </c>
       <c r="Z11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.16250000000000001</v>
       </c>
       <c r="AA11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.16785714285714287</v>
       </c>
       <c r="AB11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.17321428571428574</v>
       </c>
       <c r="AC11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.1785714285714286</v>
       </c>
       <c r="AD11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.18392857142857147</v>
       </c>
       <c r="AE11" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="38"/>
         <v>0.18928571428571433</v>
       </c>
       <c r="AF11" s="13">
-        <f t="shared" ref="AF11" si="20">AE11+$AI11</f>
+        <f t="shared" ref="AF11" si="39">AE11+$AI11</f>
         <v>0.1946428571428572</v>
       </c>
       <c r="AG11" s="13">
         <v>0.2</v>
       </c>
       <c r="AI11" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>5.3571428571428572E-3</v>
       </c>
     </row>
@@ -7738,118 +9481,118 @@
         <v>0.01</v>
       </c>
       <c r="F12" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="28"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G12" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="29"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H12" s="13">
-        <f t="shared" ref="H12:AE12" si="21">G12+$AI12</f>
+        <f t="shared" ref="H12:AE12" si="40">G12+$AI12</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE12" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="40"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF12" s="13">
-        <f t="shared" ref="AF12" si="22">AE12+$AI12</f>
+        <f t="shared" ref="AF12" si="41">AE12+$AI12</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG12" s="13">
         <v>0.1</v>
       </c>
       <c r="AI12" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -7870,118 +9613,118 @@
         <v>0.01</v>
       </c>
       <c r="F13" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="28"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G13" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="29"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H13" s="13">
-        <f t="shared" ref="H13:AE13" si="23">G13+$AI13</f>
+        <f t="shared" ref="H13:AE13" si="42">G13+$AI13</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE13" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="42"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF13" s="13">
-        <f t="shared" ref="AF13" si="24">AE13+$AI13</f>
+        <f t="shared" ref="AF13" si="43">AE13+$AI13</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG13" s="13">
         <v>0.1</v>
       </c>
       <c r="AI13" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -8002,118 +9745,118 @@
         <v>0.01</v>
       </c>
       <c r="F14" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="28"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G14" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="29"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H14" s="13">
-        <f t="shared" ref="H14:AE14" si="25">G14+$AI14</f>
+        <f t="shared" ref="H14:AE14" si="44">G14+$AI14</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE14" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="44"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF14" s="13">
-        <f t="shared" ref="AF14" si="26">AE14+$AI14</f>
+        <f t="shared" ref="AF14" si="45">AE14+$AI14</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG14" s="13">
         <v>0.1</v>
       </c>
       <c r="AI14" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -8134,118 +9877,118 @@
         <v>0.01</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="28"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="29"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" ref="H15:AE15" si="27">G15+$AI15</f>
+        <f t="shared" ref="H15:AE15" si="46">G15+$AI15</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE15" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF15" s="13">
-        <f t="shared" ref="AF15" si="28">AE15+$AI15</f>
+        <f t="shared" ref="AF15" si="47">AE15+$AI15</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG15" s="13">
         <v>0.1</v>
       </c>
       <c r="AI15" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -8266,118 +10009,118 @@
         <v>0.01</v>
       </c>
       <c r="F16" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="28"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G16" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="29"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H16" s="13">
-        <f t="shared" ref="H16:AE16" si="29">G16+$AI16</f>
+        <f t="shared" ref="H16:AE16" si="48">G16+$AI16</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE16" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF16" s="13">
-        <f t="shared" ref="AF16" si="30">AE16+$AI16</f>
+        <f t="shared" ref="AF16" si="49">AE16+$AI16</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG16" s="13">
         <v>0.1</v>
       </c>
       <c r="AI16" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -8398,118 +10141,118 @@
         <v>0.01</v>
       </c>
       <c r="F17" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="28"/>
         <v>1.3214285714285715E-2</v>
       </c>
       <c r="G17" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="29"/>
         <v>1.6428571428571431E-2</v>
       </c>
       <c r="H17" s="13">
-        <f t="shared" ref="H17:AE17" si="31">G17+$AI17</f>
+        <f t="shared" ref="H17:AE17" si="50">G17+$AI17</f>
         <v>1.9642857142857146E-2</v>
       </c>
       <c r="I17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>2.2857142857142861E-2</v>
       </c>
       <c r="J17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>2.6071428571428575E-2</v>
       </c>
       <c r="K17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>2.928571428571429E-2</v>
       </c>
       <c r="L17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="M17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="N17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>3.8928571428571423E-2</v>
       </c>
       <c r="O17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>4.2142857142857135E-2</v>
       </c>
       <c r="P17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>4.5357142857142846E-2</v>
       </c>
       <c r="Q17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>4.8571428571428557E-2</v>
       </c>
       <c r="R17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>5.1785714285714268E-2</v>
       </c>
       <c r="S17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>5.4999999999999979E-2</v>
       </c>
       <c r="T17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>5.8214285714285691E-2</v>
       </c>
       <c r="U17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>6.1428571428571402E-2</v>
       </c>
       <c r="V17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>6.4642857142857113E-2</v>
       </c>
       <c r="W17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>6.7857142857142824E-2</v>
       </c>
       <c r="X17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>7.1071428571428535E-2</v>
       </c>
       <c r="Y17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>7.4285714285714247E-2</v>
       </c>
       <c r="Z17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>7.7499999999999958E-2</v>
       </c>
       <c r="AA17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>8.0714285714285669E-2</v>
       </c>
       <c r="AB17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>8.392857142857138E-2</v>
       </c>
       <c r="AC17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>8.7142857142857091E-2</v>
       </c>
       <c r="AD17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>9.0357142857142803E-2</v>
       </c>
       <c r="AE17" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>9.3571428571428514E-2</v>
       </c>
       <c r="AF17" s="13">
-        <f t="shared" ref="AF17" si="32">AE17+$AI17</f>
+        <f t="shared" ref="AF17" si="51">AE17+$AI17</f>
         <v>9.6785714285714225E-2</v>
       </c>
       <c r="AG17" s="13">
         <v>0.1</v>
       </c>
       <c r="AI17" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>3.2142857142857147E-3</v>
       </c>
     </row>
@@ -8530,118 +10273,118 @@
         <v>0.10000000000000002</v>
       </c>
       <c r="F18" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="28"/>
         <v>0.11071428571428574</v>
       </c>
       <c r="G18" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="29"/>
         <v>0.12142857142857146</v>
       </c>
       <c r="H18" s="13">
-        <f t="shared" ref="H18:AE18" si="33">G18+$AI18</f>
+        <f t="shared" ref="H18:AE18" si="52">G18+$AI18</f>
         <v>0.13214285714285717</v>
       </c>
       <c r="I18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.14285714285714288</v>
       </c>
       <c r="J18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.15357142857142858</v>
       </c>
       <c r="K18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.16428571428571428</v>
       </c>
       <c r="L18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.17499999999999999</v>
       </c>
       <c r="M18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.18571428571428569</v>
       </c>
       <c r="N18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.1964285714285714</v>
       </c>
       <c r="O18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.2071428571428571</v>
       </c>
       <c r="P18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.2178571428571428</v>
       </c>
       <c r="Q18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.22857142857142851</v>
       </c>
       <c r="R18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.23928571428571421</v>
       </c>
       <c r="S18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.24999999999999992</v>
       </c>
       <c r="T18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.26071428571428562</v>
       </c>
       <c r="U18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.27142857142857135</v>
       </c>
       <c r="V18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.28214285714285708</v>
       </c>
       <c r="W18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.29285714285714282</v>
       </c>
       <c r="X18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.30357142857142855</v>
       </c>
       <c r="Y18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.31428571428571428</v>
       </c>
       <c r="Z18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="AA18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.33571428571428574</v>
       </c>
       <c r="AB18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.34642857142857147</v>
       </c>
       <c r="AC18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.35714285714285721</v>
       </c>
       <c r="AD18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.36785714285714294</v>
       </c>
       <c r="AE18" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="52"/>
         <v>0.37857142857142867</v>
       </c>
       <c r="AF18" s="13">
-        <f t="shared" ref="AF18" si="34">AE18+$AI18</f>
+        <f t="shared" ref="AF18" si="53">AE18+$AI18</f>
         <v>0.3892857142857144</v>
       </c>
       <c r="AG18" s="13">
         <v>0.4</v>
       </c>
       <c r="AI18" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>1.0714285714285714E-2</v>
       </c>
     </row>
@@ -8650,7 +10393,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F1D9CA-EF31-4EFC-AD7B-988A295063BD}">
   <dimension ref="A1:AI18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9039,122 +10782,95 @@
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="E4" s="13">
-        <v>0.10000000000000002</v>
+        <v>9.999999999999995E-2</v>
       </c>
       <c r="F4" s="13">
-        <f t="shared" si="1"/>
-        <v>0.16785714285714287</v>
+        <v>0.18571428571428567</v>
       </c>
       <c r="G4" s="13">
-        <f t="shared" si="1"/>
-        <v>0.23571428571428571</v>
+        <v>0.27142857142857135</v>
       </c>
       <c r="H4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.30357142857142855</v>
+        <v>0.3571428571428571</v>
       </c>
       <c r="I4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.37142857142857139</v>
+        <v>0.44285714285714284</v>
       </c>
       <c r="J4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.43928571428571422</v>
+        <v>0.52857142857142847</v>
       </c>
       <c r="K4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.50714285714285712</v>
+        <v>0.61428571428571421</v>
       </c>
       <c r="L4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.57499999999999996</v>
+        <v>0.7</v>
       </c>
       <c r="M4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.64285714285714279</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="N4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.71071428571428563</v>
+        <v>0.87142857142857144</v>
       </c>
       <c r="O4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.77857142857142847</v>
+        <v>0.95714285714285707</v>
       </c>
       <c r="P4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.84642857142857131</v>
+        <v>1.0428571428571427</v>
       </c>
       <c r="Q4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.91428571428571415</v>
+        <v>1.1285714285714286</v>
       </c>
       <c r="R4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.98214285714285698</v>
+        <v>1.2142857142857142</v>
       </c>
       <c r="S4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.0499999999999998</v>
+        <v>1.3</v>
       </c>
       <c r="T4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.1178571428571427</v>
+        <v>1.3857142857142857</v>
       </c>
       <c r="U4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.1857142857142855</v>
+        <v>1.4714285714285713</v>
       </c>
       <c r="V4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.2535714285714283</v>
+        <v>1.5571428571428572</v>
       </c>
       <c r="W4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.3214285714285712</v>
+        <v>1.6428571428571428</v>
       </c>
       <c r="X4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.389285714285714</v>
+        <v>1.7285714285714286</v>
       </c>
       <c r="Y4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.4571428571428569</v>
+        <v>1.8142857142857143</v>
       </c>
       <c r="Z4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.5249999999999997</v>
+        <v>1.9</v>
       </c>
       <c r="AA4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.5928571428571425</v>
+        <v>1.9857142857142858</v>
       </c>
       <c r="AB4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.6607142857142854</v>
+        <v>2.0714285714285712</v>
       </c>
       <c r="AC4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.7285714285714282</v>
+        <v>2.157142857142857</v>
       </c>
       <c r="AD4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.796428571428571</v>
+        <v>2.2428571428571429</v>
       </c>
       <c r="AE4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.8642857142857139</v>
+        <v>2.3285714285714287</v>
       </c>
       <c r="AF4" s="13">
-        <f t="shared" si="0"/>
-        <v>1.9321428571428567</v>
+        <v>2.4142857142857141</v>
       </c>
       <c r="AG4" s="13">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" s="28">
         <f t="shared" si="2"/>
-        <v>6.7857142857142852E-2</v>
+        <v>8.5714285714285715E-2</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.3">
@@ -9165,392 +10881,338 @@
         <v>0</v>
       </c>
       <c r="C5" s="27">
-        <v>0.01</v>
+        <v>1.6666666666666663E-2</v>
       </c>
       <c r="D5" s="27">
-        <v>0.01</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="E5" s="27">
-        <v>0.01</v>
+        <v>5.000000000000001E-2</v>
       </c>
       <c r="F5" s="13">
-        <f t="shared" si="1"/>
-        <v>2.7499999999999997E-2</v>
+        <f t="shared" ref="F5" si="3">E5+$AI5</f>
+        <v>8.3928571428571436E-2</v>
       </c>
       <c r="G5" s="13">
-        <f t="shared" si="1"/>
-        <v>4.4999999999999998E-2</v>
+        <f t="shared" ref="G5" si="4">F5+$AI5</f>
+        <v>0.11785714285714285</v>
       </c>
       <c r="H5" s="13">
-        <f t="shared" si="0"/>
-        <v>6.25E-2</v>
+        <f t="shared" ref="H5" si="5">G5+$AI5</f>
+        <v>0.15178571428571427</v>
       </c>
       <c r="I5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.08</v>
+        <f t="shared" ref="I5" si="6">H5+$AI5</f>
+        <v>0.18571428571428569</v>
       </c>
       <c r="J5" s="13">
-        <f t="shared" si="0"/>
-        <v>9.7500000000000003E-2</v>
+        <f t="shared" ref="J5" si="7">I5+$AI5</f>
+        <v>0.21964285714285711</v>
       </c>
       <c r="K5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.115</v>
+        <f t="shared" ref="K5" si="8">J5+$AI5</f>
+        <v>0.25357142857142856</v>
       </c>
       <c r="L5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.13250000000000001</v>
+        <f t="shared" ref="L5" si="9">K5+$AI5</f>
+        <v>0.28749999999999998</v>
       </c>
       <c r="M5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.15</v>
+        <f t="shared" ref="M5" si="10">L5+$AI5</f>
+        <v>0.3214285714285714</v>
       </c>
       <c r="N5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.16749999999999998</v>
+        <f t="shared" ref="N5" si="11">M5+$AI5</f>
+        <v>0.35535714285714282</v>
       </c>
       <c r="O5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.18499999999999997</v>
+        <f t="shared" ref="O5" si="12">N5+$AI5</f>
+        <v>0.38928571428571423</v>
       </c>
       <c r="P5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.20249999999999996</v>
+        <f t="shared" ref="P5" si="13">O5+$AI5</f>
+        <v>0.42321428571428565</v>
       </c>
       <c r="Q5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.21999999999999995</v>
+        <f t="shared" ref="Q5" si="14">P5+$AI5</f>
+        <v>0.45714285714285707</v>
       </c>
       <c r="R5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.23749999999999993</v>
+        <f t="shared" ref="R5" si="15">Q5+$AI5</f>
+        <v>0.49107142857142849</v>
       </c>
       <c r="S5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.25499999999999995</v>
+        <f t="shared" ref="S5" si="16">R5+$AI5</f>
+        <v>0.52499999999999991</v>
       </c>
       <c r="T5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.27249999999999996</v>
+        <f t="shared" ref="T5" si="17">S5+$AI5</f>
+        <v>0.55892857142857133</v>
       </c>
       <c r="U5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.28999999999999998</v>
+        <f t="shared" ref="U5" si="18">T5+$AI5</f>
+        <v>0.59285714285714275</v>
       </c>
       <c r="V5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.3075</v>
+        <f t="shared" ref="V5" si="19">U5+$AI5</f>
+        <v>0.62678571428571417</v>
       </c>
       <c r="W5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.32500000000000001</v>
+        <f t="shared" ref="W5" si="20">V5+$AI5</f>
+        <v>0.66071428571428559</v>
       </c>
       <c r="X5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.34250000000000003</v>
+        <f t="shared" ref="X5" si="21">W5+$AI5</f>
+        <v>0.69464285714285701</v>
       </c>
       <c r="Y5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
+        <f t="shared" ref="Y5" si="22">X5+$AI5</f>
+        <v>0.72857142857142843</v>
       </c>
       <c r="Z5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.37750000000000006</v>
+        <f t="shared" ref="Z5" si="23">Y5+$AI5</f>
+        <v>0.76249999999999984</v>
       </c>
       <c r="AA5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.39500000000000007</v>
+        <f t="shared" ref="AA5" si="24">Z5+$AI5</f>
+        <v>0.79642857142857126</v>
       </c>
       <c r="AB5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.41250000000000009</v>
+        <f t="shared" ref="AB5" si="25">AA5+$AI5</f>
+        <v>0.83035714285714268</v>
       </c>
       <c r="AC5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.4300000000000001</v>
+        <f t="shared" ref="AC5" si="26">AB5+$AI5</f>
+        <v>0.8642857142857141</v>
       </c>
       <c r="AD5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.44750000000000012</v>
+        <f t="shared" ref="AD5" si="27">AC5+$AI5</f>
+        <v>0.89821428571428552</v>
       </c>
       <c r="AE5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.46500000000000014</v>
+        <f t="shared" ref="AE5" si="28">AD5+$AI5</f>
+        <v>0.93214285714285694</v>
       </c>
       <c r="AF5" s="13">
-        <f t="shared" si="0"/>
-        <v>0.48250000000000015</v>
+        <f t="shared" ref="AF5" si="29">AE5+$AI5</f>
+        <v>0.96607142857142836</v>
       </c>
       <c r="AG5" s="13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AI5" s="28">
         <f t="shared" si="2"/>
-        <v>1.7499999999999998E-2</v>
+        <v>3.3928571428571426E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
+    <row r="6" spans="1:35" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="31">
         <v>0</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="27">
         <v>1E-4</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="27">
         <v>1E-4</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="27">
+        <v>9.9999999999995925E-5</v>
+      </c>
+      <c r="F6" s="27">
+        <v>3.6678571428571394E-3</v>
+      </c>
+      <c r="G6" s="27">
+        <v>7.2357142857142828E-3</v>
+      </c>
+      <c r="H6" s="27">
+        <v>1.0803571428571426E-2</v>
+      </c>
+      <c r="I6" s="27">
+        <v>1.437142857142857E-2</v>
+      </c>
+      <c r="J6" s="27">
+        <v>1.7939285714285713E-2</v>
+      </c>
+      <c r="K6" s="27">
+        <v>2.1507142857142857E-2</v>
+      </c>
+      <c r="L6" s="27">
+        <v>2.5075E-2</v>
+      </c>
+      <c r="M6" s="27">
+        <v>2.8642857142857144E-2</v>
+      </c>
+      <c r="N6" s="27">
+        <v>3.2210714285714287E-2</v>
+      </c>
+      <c r="O6" s="27">
+        <v>3.577857142857143E-2</v>
+      </c>
+      <c r="P6" s="27">
+        <v>3.9346428571428574E-2</v>
+      </c>
+      <c r="Q6" s="27">
+        <v>4.2914285714285717E-2</v>
+      </c>
+      <c r="R6" s="27">
+        <v>4.6482142857142861E-2</v>
+      </c>
+      <c r="S6" s="27">
+        <v>5.0050000000000004E-2</v>
+      </c>
+      <c r="T6" s="27">
+        <v>5.3617857142857148E-2</v>
+      </c>
+      <c r="U6" s="27">
+        <v>5.7185714285714291E-2</v>
+      </c>
+      <c r="V6" s="27">
+        <v>6.0753571428571435E-2</v>
+      </c>
+      <c r="W6" s="27">
+        <v>6.4321428571428571E-2</v>
+      </c>
+      <c r="X6" s="27">
+        <v>6.7889285714285721E-2</v>
+      </c>
+      <c r="Y6" s="27">
+        <v>7.1457142857142872E-2</v>
+      </c>
+      <c r="Z6" s="27">
+        <v>7.5025000000000008E-2</v>
+      </c>
+      <c r="AA6" s="27">
+        <v>7.8592857142857145E-2</v>
+      </c>
+      <c r="AB6" s="27">
+        <v>8.2160714285714295E-2</v>
+      </c>
+      <c r="AC6" s="27">
+        <v>8.5728571428571446E-2</v>
+      </c>
+      <c r="AD6" s="27">
+        <v>8.9296428571428582E-2</v>
+      </c>
+      <c r="AE6" s="27">
+        <v>9.2864285714285719E-2</v>
+      </c>
+      <c r="AF6" s="27">
+        <v>9.6432142857142869E-2</v>
+      </c>
+      <c r="AG6" s="27">
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="AI6" s="33">
+        <f t="shared" si="2"/>
+        <v>3.5678571428571434E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="31">
+        <v>0</v>
+      </c>
+      <c r="C7" s="27">
         <v>1E-4</v>
       </c>
-      <c r="F6" s="32">
-        <f t="shared" ref="F6" si="3">E6+$AI6</f>
-        <v>1.8821428571428572E-3</v>
-      </c>
-      <c r="G6" s="32">
-        <f t="shared" ref="G6:AF6" si="4">F6+$AI6</f>
-        <v>3.6642857142857145E-3</v>
-      </c>
-      <c r="H6" s="32">
-        <f t="shared" si="4"/>
-        <v>5.4464285714285717E-3</v>
-      </c>
-      <c r="I6" s="32">
-        <f t="shared" si="4"/>
-        <v>7.2285714285714288E-3</v>
-      </c>
-      <c r="J6" s="32">
-        <f t="shared" si="4"/>
-        <v>9.0107142857142851E-3</v>
-      </c>
-      <c r="K6" s="32">
-        <f t="shared" si="4"/>
-        <v>1.0792857142857142E-2</v>
-      </c>
-      <c r="L6" s="32">
-        <f t="shared" si="4"/>
-        <v>1.2574999999999999E-2</v>
-      </c>
-      <c r="M6" s="32">
-        <f t="shared" si="4"/>
-        <v>1.4357142857142857E-2</v>
-      </c>
-      <c r="N6" s="32">
-        <f t="shared" si="4"/>
-        <v>1.6139285714285714E-2</v>
-      </c>
-      <c r="O6" s="32">
-        <f t="shared" si="4"/>
-        <v>1.7921428571428571E-2</v>
-      </c>
-      <c r="P6" s="32">
-        <f t="shared" si="4"/>
-        <v>1.9703571428571428E-2</v>
-      </c>
-      <c r="Q6" s="32">
-        <f t="shared" si="4"/>
-        <v>2.1485714285714285E-2</v>
-      </c>
-      <c r="R6" s="32">
-        <f t="shared" si="4"/>
-        <v>2.3267857142857142E-2</v>
-      </c>
-      <c r="S6" s="32">
-        <f t="shared" si="4"/>
-        <v>2.5049999999999999E-2</v>
-      </c>
-      <c r="T6" s="32">
-        <f t="shared" si="4"/>
-        <v>2.6832142857142856E-2</v>
-      </c>
-      <c r="U6" s="32">
-        <f t="shared" si="4"/>
-        <v>2.8614285714285714E-2</v>
-      </c>
-      <c r="V6" s="32">
-        <f t="shared" si="4"/>
-        <v>3.0396428571428571E-2</v>
-      </c>
-      <c r="W6" s="32">
-        <f t="shared" si="4"/>
-        <v>3.2178571428571431E-2</v>
-      </c>
-      <c r="X6" s="32">
-        <f t="shared" si="4"/>
-        <v>3.3960714285714289E-2</v>
-      </c>
-      <c r="Y6" s="32">
-        <f t="shared" si="4"/>
-        <v>3.5742857142857146E-2</v>
-      </c>
-      <c r="Z6" s="32">
-        <f t="shared" si="4"/>
-        <v>3.7525000000000003E-2</v>
-      </c>
-      <c r="AA6" s="32">
-        <f t="shared" si="4"/>
-        <v>3.930714285714286E-2</v>
-      </c>
-      <c r="AB6" s="32">
-        <f t="shared" si="4"/>
-        <v>4.1089285714285717E-2</v>
-      </c>
-      <c r="AC6" s="32">
-        <f t="shared" si="4"/>
-        <v>4.2871428571428574E-2</v>
-      </c>
-      <c r="AD6" s="32">
-        <f t="shared" si="4"/>
-        <v>4.4653571428571431E-2</v>
-      </c>
-      <c r="AE6" s="32">
-        <f t="shared" si="4"/>
-        <v>4.6435714285714288E-2</v>
-      </c>
-      <c r="AF6" s="32">
-        <f t="shared" si="4"/>
-        <v>4.8217857142857146E-2</v>
-      </c>
-      <c r="AG6" s="32">
-        <v>0.05</v>
-      </c>
-      <c r="AI6" s="28">
-        <f t="shared" si="2"/>
-        <v>1.7821428571428571E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A7" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="30">
+      <c r="D7" s="27">
         <v>1E-4</v>
       </c>
-      <c r="D7" s="30">
+      <c r="E7" s="27">
         <v>1E-4</v>
       </c>
-      <c r="E7" s="30">
-        <v>1E-4</v>
-      </c>
-      <c r="F7" s="32">
-        <f t="shared" si="1"/>
-        <v>1.8821428571428572E-3</v>
-      </c>
-      <c r="G7" s="32">
-        <f t="shared" si="1"/>
-        <v>3.6642857142857145E-3</v>
-      </c>
-      <c r="H7" s="32">
-        <f t="shared" si="0"/>
-        <v>5.4464285714285717E-3</v>
-      </c>
-      <c r="I7" s="32">
-        <f t="shared" si="0"/>
-        <v>7.2285714285714288E-3</v>
-      </c>
-      <c r="J7" s="32">
-        <f t="shared" si="0"/>
-        <v>9.0107142857142851E-3</v>
-      </c>
-      <c r="K7" s="32">
-        <f t="shared" si="0"/>
-        <v>1.0792857142857142E-2</v>
-      </c>
-      <c r="L7" s="32">
-        <f t="shared" si="0"/>
-        <v>1.2574999999999999E-2</v>
-      </c>
-      <c r="M7" s="32">
-        <f t="shared" si="0"/>
-        <v>1.4357142857142857E-2</v>
-      </c>
-      <c r="N7" s="32">
-        <f t="shared" si="0"/>
-        <v>1.6139285714285714E-2</v>
-      </c>
-      <c r="O7" s="32">
-        <f t="shared" si="0"/>
-        <v>1.7921428571428571E-2</v>
-      </c>
-      <c r="P7" s="32">
-        <f t="shared" si="0"/>
-        <v>1.9703571428571428E-2</v>
-      </c>
-      <c r="Q7" s="32">
-        <f t="shared" si="0"/>
-        <v>2.1485714285714285E-2</v>
-      </c>
-      <c r="R7" s="32">
-        <f t="shared" si="0"/>
-        <v>2.3267857142857142E-2</v>
-      </c>
-      <c r="S7" s="32">
-        <f t="shared" si="0"/>
-        <v>2.5049999999999999E-2</v>
-      </c>
-      <c r="T7" s="32">
-        <f t="shared" si="0"/>
-        <v>2.6832142857142856E-2</v>
-      </c>
-      <c r="U7" s="32">
-        <f t="shared" si="0"/>
-        <v>2.8614285714285714E-2</v>
-      </c>
-      <c r="V7" s="32">
-        <f t="shared" si="0"/>
-        <v>3.0396428571428571E-2</v>
-      </c>
-      <c r="W7" s="32">
-        <f t="shared" si="0"/>
-        <v>3.2178571428571431E-2</v>
-      </c>
-      <c r="X7" s="32">
-        <f t="shared" si="0"/>
-        <v>3.3960714285714289E-2</v>
-      </c>
-      <c r="Y7" s="32">
-        <f t="shared" si="0"/>
-        <v>3.5742857142857146E-2</v>
-      </c>
-      <c r="Z7" s="32">
-        <f t="shared" si="0"/>
-        <v>3.7525000000000003E-2</v>
-      </c>
-      <c r="AA7" s="32">
-        <f t="shared" si="0"/>
-        <v>3.930714285714286E-2</v>
-      </c>
-      <c r="AB7" s="32">
-        <f t="shared" si="0"/>
-        <v>4.1089285714285717E-2</v>
-      </c>
-      <c r="AC7" s="32">
-        <f t="shared" si="0"/>
-        <v>4.2871428571428574E-2</v>
-      </c>
-      <c r="AD7" s="32">
-        <f t="shared" si="0"/>
-        <v>4.4653571428571431E-2</v>
-      </c>
-      <c r="AE7" s="32">
-        <f t="shared" si="0"/>
-        <v>4.6435714285714288E-2</v>
-      </c>
-      <c r="AF7" s="32">
-        <f t="shared" si="0"/>
-        <v>4.8217857142857146E-2</v>
-      </c>
-      <c r="AG7" s="32">
-        <v>0.05</v>
-      </c>
-      <c r="AI7" s="28">
-        <f t="shared" si="2"/>
-        <v>1.7821428571428571E-3</v>
+      <c r="F7" s="27">
+        <v>3.6678599999999998E-3</v>
+      </c>
+      <c r="G7" s="27">
+        <v>7.2357100000000002E-3</v>
+      </c>
+      <c r="H7" s="27">
+        <v>1.08036E-2</v>
+      </c>
+      <c r="I7" s="27">
+        <v>1.4371399999999999E-2</v>
+      </c>
+      <c r="J7" s="27">
+        <v>1.7939299999999998E-2</v>
+      </c>
+      <c r="K7" s="27">
+        <v>2.1507100000000001E-2</v>
+      </c>
+      <c r="L7" s="27">
+        <v>2.5075E-2</v>
+      </c>
+      <c r="M7" s="27">
+        <v>2.8642899999999999E-2</v>
+      </c>
+      <c r="N7" s="27">
+        <v>3.2210700000000002E-2</v>
+      </c>
+      <c r="O7" s="27">
+        <v>3.5778600000000001E-2</v>
+      </c>
+      <c r="P7" s="27">
+        <v>3.9346399999999997E-2</v>
+      </c>
+      <c r="Q7" s="27">
+        <v>4.2914300000000002E-2</v>
+      </c>
+      <c r="R7" s="27">
+        <v>4.6482099999999998E-2</v>
+      </c>
+      <c r="S7" s="27">
+        <v>5.0049999999999997E-2</v>
+      </c>
+      <c r="T7" s="27">
+        <v>5.3617900000000003E-2</v>
+      </c>
+      <c r="U7" s="27">
+        <v>5.7185699999999999E-2</v>
+      </c>
+      <c r="V7" s="27">
+        <v>6.0753599999999998E-2</v>
+      </c>
+      <c r="W7" s="27">
+        <v>6.4321400000000001E-2</v>
+      </c>
+      <c r="X7" s="27">
+        <v>6.78893E-2</v>
+      </c>
+      <c r="Y7" s="27">
+        <v>7.1457099999999996E-2</v>
+      </c>
+      <c r="Z7" s="27">
+        <v>7.5024999999999994E-2</v>
+      </c>
+      <c r="AA7" s="27">
+        <v>7.8592899999999993E-2</v>
+      </c>
+      <c r="AB7" s="27">
+        <v>8.2160700000000003E-2</v>
+      </c>
+      <c r="AC7" s="27">
+        <v>8.5728600000000002E-2</v>
+      </c>
+      <c r="AD7" s="27">
+        <v>8.9296399999999998E-2</v>
+      </c>
+      <c r="AE7" s="27">
+        <v>9.2864299999999997E-2</v>
+      </c>
+      <c r="AF7" s="27">
+        <v>9.6432100000000007E-2</v>
+      </c>
+      <c r="AG7" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="AI7" s="33">
+        <f t="shared" si="2"/>
+        <v>3.567857142857143E-3</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.3">
@@ -9571,118 +11233,118 @@
       </c>
       <c r="F8" s="13">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <v>0.2821428571428572</v>
       </c>
       <c r="G8" s="13">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.36428571428571432</v>
       </c>
       <c r="H8" s="13">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.44642857142857145</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.52857142857142858</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.61071428571428577</v>
       </c>
       <c r="K8" s="13">
         <f t="shared" si="0"/>
-        <v>0.79999999999999993</v>
+        <v>0.69285714285714295</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.77500000000000013</v>
       </c>
       <c r="M8" s="13">
         <f t="shared" si="0"/>
-        <v>0.99999999999999989</v>
+        <v>0.85714285714285732</v>
       </c>
       <c r="N8" s="13">
         <f t="shared" si="0"/>
-        <v>1.0999999999999999</v>
+        <v>0.9392857142857145</v>
       </c>
       <c r="O8" s="13">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.0214285714285716</v>
       </c>
       <c r="P8" s="13">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1.1035714285714286</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="0"/>
-        <v>1.4000000000000001</v>
+        <v>1.1857142857142857</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="0"/>
-        <v>1.5000000000000002</v>
+        <v>1.2678571428571428</v>
       </c>
       <c r="S8" s="13">
         <f t="shared" si="0"/>
-        <v>1.6000000000000003</v>
+        <v>1.3499999999999999</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="0"/>
-        <v>1.7000000000000004</v>
+        <v>1.4321428571428569</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="0"/>
-        <v>1.8000000000000005</v>
+        <v>1.514285714285714</v>
       </c>
       <c r="V8" s="13">
         <f t="shared" si="0"/>
-        <v>1.9000000000000006</v>
+        <v>1.5964285714285711</v>
       </c>
       <c r="W8" s="13">
         <f t="shared" si="0"/>
-        <v>2.0000000000000004</v>
+        <v>1.6785714285714282</v>
       </c>
       <c r="X8" s="13">
         <f t="shared" si="0"/>
-        <v>2.1000000000000005</v>
+        <v>1.7607142857142852</v>
       </c>
       <c r="Y8" s="13">
         <f t="shared" si="0"/>
-        <v>2.2000000000000006</v>
+        <v>1.8428571428571423</v>
       </c>
       <c r="Z8" s="13">
         <f t="shared" si="0"/>
-        <v>2.3000000000000007</v>
+        <v>1.9249999999999994</v>
       </c>
       <c r="AA8" s="13">
         <f t="shared" si="0"/>
-        <v>2.4000000000000008</v>
+        <v>2.0071428571428567</v>
       </c>
       <c r="AB8" s="13">
         <f t="shared" si="0"/>
-        <v>2.5000000000000009</v>
+        <v>2.089285714285714</v>
       </c>
       <c r="AC8" s="13">
         <f t="shared" si="0"/>
-        <v>2.600000000000001</v>
+        <v>2.1714285714285713</v>
       </c>
       <c r="AD8" s="13">
         <f t="shared" si="0"/>
-        <v>2.7000000000000011</v>
+        <v>2.2535714285714286</v>
       </c>
       <c r="AE8" s="13">
         <f t="shared" si="0"/>
-        <v>2.8000000000000012</v>
+        <v>2.3357142857142859</v>
       </c>
       <c r="AF8" s="13">
         <f t="shared" si="0"/>
-        <v>2.9000000000000012</v>
+        <v>2.4178571428571431</v>
       </c>
       <c r="AG8" s="13">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AI8" s="28">
         <f t="shared" si="2"/>
-        <v>9.9999999999999992E-2</v>
+        <v>8.2142857142857142E-2</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.3">
@@ -9835,118 +11497,118 @@
       </c>
       <c r="F10" s="13">
         <f t="shared" si="1"/>
-        <v>0.52857142857142869</v>
+        <v>0.47500000000000009</v>
       </c>
       <c r="G10" s="13">
         <f t="shared" si="1"/>
-        <v>0.65714285714285725</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H10" s="13">
         <f t="shared" si="0"/>
-        <v>0.78571428571428581</v>
+        <v>0.625</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.91428571428571437</v>
+        <v>0.7</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>1.0428571428571429</v>
+        <v>0.77499999999999991</v>
       </c>
       <c r="K10" s="13">
         <f t="shared" si="0"/>
-        <v>1.1714285714285715</v>
+        <v>0.84999999999999987</v>
       </c>
       <c r="L10" s="13">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>0.92499999999999982</v>
       </c>
       <c r="M10" s="13">
         <f t="shared" si="0"/>
-        <v>1.4285714285714286</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="N10" s="13">
         <f t="shared" si="0"/>
-        <v>1.5571428571428572</v>
+        <v>1.0749999999999997</v>
       </c>
       <c r="O10" s="13">
         <f t="shared" si="0"/>
-        <v>1.6857142857142857</v>
+        <v>1.1499999999999997</v>
       </c>
       <c r="P10" s="13">
         <f t="shared" si="0"/>
-        <v>1.8142857142857143</v>
+        <v>1.2249999999999996</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="0"/>
-        <v>1.9428571428571428</v>
+        <v>1.2999999999999996</v>
       </c>
       <c r="R10" s="13">
         <f t="shared" si="0"/>
-        <v>2.0714285714285716</v>
+        <v>1.3749999999999996</v>
       </c>
       <c r="S10" s="13">
         <f t="shared" si="0"/>
-        <v>2.2000000000000002</v>
+        <v>1.4499999999999995</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="0"/>
-        <v>2.3285714285714287</v>
+        <v>1.5249999999999995</v>
       </c>
       <c r="U10" s="13">
         <f t="shared" si="0"/>
-        <v>2.4571428571428573</v>
+        <v>1.5999999999999994</v>
       </c>
       <c r="V10" s="13">
         <f t="shared" si="0"/>
-        <v>2.5857142857142859</v>
+        <v>1.6749999999999994</v>
       </c>
       <c r="W10" s="13">
         <f t="shared" si="0"/>
-        <v>2.7142857142857144</v>
+        <v>1.7499999999999993</v>
       </c>
       <c r="X10" s="13">
         <f t="shared" si="0"/>
-        <v>2.842857142857143</v>
+        <v>1.8249999999999993</v>
       </c>
       <c r="Y10" s="13">
         <f t="shared" si="0"/>
-        <v>2.9714285714285715</v>
+        <v>1.8999999999999992</v>
       </c>
       <c r="Z10" s="13">
         <f t="shared" si="0"/>
-        <v>3.1</v>
+        <v>1.9749999999999992</v>
       </c>
       <c r="AA10" s="13">
         <f t="shared" si="0"/>
-        <v>3.2285714285714286</v>
+        <v>2.0499999999999994</v>
       </c>
       <c r="AB10" s="13">
         <f t="shared" si="0"/>
-        <v>3.3571428571428572</v>
+        <v>2.1249999999999996</v>
       </c>
       <c r="AC10" s="13">
         <f t="shared" si="0"/>
-        <v>3.4857142857142858</v>
+        <v>2.1999999999999997</v>
       </c>
       <c r="AD10" s="13">
         <f t="shared" si="0"/>
-        <v>3.6142857142857143</v>
+        <v>2.2749999999999999</v>
       </c>
       <c r="AE10" s="13">
         <f t="shared" si="0"/>
-        <v>3.7428571428571429</v>
+        <v>2.35</v>
       </c>
       <c r="AF10" s="13">
         <f t="shared" si="0"/>
-        <v>3.8714285714285714</v>
+        <v>2.4250000000000003</v>
       </c>
       <c r="AG10" s="13">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AI10" s="28">
         <f t="shared" si="2"/>
-        <v>0.12857142857142859</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.3">
@@ -10126,83 +11788,83 @@
         <v>0.13250000000000001</v>
       </c>
       <c r="M12" s="13">
-        <f t="shared" ref="M12:AF18" si="5">L12+$AI12</f>
+        <f t="shared" ref="M12:AF18" si="30">L12+$AI12</f>
         <v>0.15</v>
       </c>
       <c r="N12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.16749999999999998</v>
       </c>
       <c r="O12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.18499999999999997</v>
       </c>
       <c r="P12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.20249999999999996</v>
       </c>
       <c r="Q12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.21999999999999995</v>
       </c>
       <c r="R12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.23749999999999993</v>
       </c>
       <c r="S12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.25499999999999995</v>
       </c>
       <c r="T12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.27249999999999996</v>
       </c>
       <c r="U12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="V12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.3075</v>
       </c>
       <c r="W12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG12" s="13">
@@ -10294,47 +11956,47 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="V13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.3075</v>
       </c>
       <c r="W13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG13" s="13">
@@ -10426,47 +12088,47 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="V14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.3075</v>
       </c>
       <c r="W14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG14" s="13">
@@ -10558,47 +12220,47 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="V15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.3075</v>
       </c>
       <c r="W15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG15" s="13">
@@ -10690,47 +12352,47 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="V16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.3075</v>
       </c>
       <c r="W16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG16" s="13">
@@ -10822,47 +12484,47 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="V17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.3075</v>
       </c>
       <c r="W17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="X17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.34250000000000003</v>
       </c>
       <c r="Y17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="Z17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.37750000000000006</v>
       </c>
       <c r="AA17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.39500000000000007</v>
       </c>
       <c r="AB17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.41250000000000009</v>
       </c>
       <c r="AC17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.4300000000000001</v>
       </c>
       <c r="AD17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.44750000000000012</v>
       </c>
       <c r="AE17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.46500000000000014</v>
       </c>
       <c r="AF17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>0.48250000000000015</v>
       </c>
       <c r="AG17" s="13">
@@ -10891,118 +12553,118 @@
       </c>
       <c r="F18" s="13">
         <f t="shared" si="1"/>
-        <v>0.16785714285714287</v>
+        <v>0.18571428571428572</v>
       </c>
       <c r="G18" s="13">
         <f t="shared" si="1"/>
-        <v>0.23571428571428571</v>
+        <v>0.27142857142857146</v>
       </c>
       <c r="H18" s="13">
         <f t="shared" si="1"/>
-        <v>0.30357142857142855</v>
+        <v>0.35714285714285721</v>
       </c>
       <c r="I18" s="13">
         <f t="shared" si="1"/>
-        <v>0.37142857142857139</v>
+        <v>0.44285714285714295</v>
       </c>
       <c r="J18" s="13">
         <f t="shared" si="1"/>
-        <v>0.43928571428571422</v>
+        <v>0.52857142857142869</v>
       </c>
       <c r="K18" s="13">
         <f t="shared" si="1"/>
-        <v>0.50714285714285712</v>
+        <v>0.61428571428571443</v>
       </c>
       <c r="L18" s="13">
         <f t="shared" si="1"/>
-        <v>0.57499999999999996</v>
+        <v>0.70000000000000018</v>
       </c>
       <c r="M18" s="13">
         <f t="shared" si="1"/>
-        <v>0.64285714285714279</v>
+        <v>0.78571428571428592</v>
       </c>
       <c r="N18" s="13">
         <f t="shared" si="1"/>
-        <v>0.71071428571428563</v>
+        <v>0.87142857142857166</v>
       </c>
       <c r="O18" s="13">
         <f t="shared" si="1"/>
-        <v>0.77857142857142847</v>
+        <v>0.95714285714285741</v>
       </c>
       <c r="P18" s="13">
         <f t="shared" si="1"/>
-        <v>0.84642857142857131</v>
+        <v>1.0428571428571431</v>
       </c>
       <c r="Q18" s="13">
         <f t="shared" si="1"/>
-        <v>0.91428571428571415</v>
+        <v>1.1285714285714288</v>
       </c>
       <c r="R18" s="13">
         <f t="shared" si="1"/>
-        <v>0.98214285714285698</v>
+        <v>1.2142857142857144</v>
       </c>
       <c r="S18" s="13">
         <f t="shared" si="1"/>
-        <v>1.0499999999999998</v>
+        <v>1.3</v>
       </c>
       <c r="T18" s="13">
         <f t="shared" si="1"/>
-        <v>1.1178571428571427</v>
+        <v>1.3857142857142857</v>
       </c>
       <c r="U18" s="13">
         <f t="shared" si="1"/>
-        <v>1.1857142857142855</v>
+        <v>1.4714285714285713</v>
       </c>
       <c r="V18" s="13">
-        <f t="shared" si="5"/>
-        <v>1.2535714285714283</v>
+        <f t="shared" si="30"/>
+        <v>1.5571428571428569</v>
       </c>
       <c r="W18" s="13">
-        <f t="shared" si="5"/>
-        <v>1.3214285714285712</v>
+        <f t="shared" si="30"/>
+        <v>1.6428571428571426</v>
       </c>
       <c r="X18" s="13">
-        <f t="shared" si="5"/>
-        <v>1.389285714285714</v>
+        <f t="shared" si="30"/>
+        <v>1.7285714285714282</v>
       </c>
       <c r="Y18" s="13">
-        <f t="shared" si="5"/>
-        <v>1.4571428571428569</v>
+        <f t="shared" si="30"/>
+        <v>1.8142857142857138</v>
       </c>
       <c r="Z18" s="13">
-        <f t="shared" si="5"/>
-        <v>1.5249999999999997</v>
+        <f t="shared" si="30"/>
+        <v>1.8999999999999995</v>
       </c>
       <c r="AA18" s="13">
-        <f t="shared" si="5"/>
-        <v>1.5928571428571425</v>
+        <f t="shared" si="30"/>
+        <v>1.9857142857142851</v>
       </c>
       <c r="AB18" s="13">
-        <f t="shared" si="5"/>
-        <v>1.6607142857142854</v>
+        <f t="shared" si="30"/>
+        <v>2.0714285714285707</v>
       </c>
       <c r="AC18" s="13">
-        <f t="shared" si="5"/>
-        <v>1.7285714285714282</v>
+        <f t="shared" si="30"/>
+        <v>2.1571428571428566</v>
       </c>
       <c r="AD18" s="13">
-        <f t="shared" si="5"/>
-        <v>1.796428571428571</v>
+        <f t="shared" si="30"/>
+        <v>2.2428571428571424</v>
       </c>
       <c r="AE18" s="13">
-        <f t="shared" si="5"/>
-        <v>1.8642857142857139</v>
+        <f t="shared" si="30"/>
+        <v>2.3285714285714283</v>
       </c>
       <c r="AF18" s="13">
-        <f t="shared" si="5"/>
-        <v>1.9321428571428567</v>
+        <f t="shared" si="30"/>
+        <v>2.4142857142857141</v>
       </c>
       <c r="AG18" s="13">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AI18" s="28">
         <f t="shared" si="2"/>
-        <v>6.7857142857142852E-2</v>
+        <v>8.5714285714285715E-2</v>
       </c>
     </row>
   </sheetData>
@@ -11010,7 +12672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF6AC21A-7770-4760-8D5B-5F2CE7B41329}">
   <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13312,7 +14974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98116DE7-D39F-483D-A3D2-93FE4B254E46}">
   <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -15614,7 +17276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F0BF70-BEB3-4C23-BA28-705EDE33B68E}">
   <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -17916,7 +19578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B36736F-CC09-489B-B698-2F45B1A52627}">
   <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -20218,7 +21880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B12D2D-5736-4639-9315-A9C245758862}">
   <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/2.RD_CGE/Input_w-t/Projection.xlsx
+++ b/2.RD_CGE/Input_w-t/Projection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_w-t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5E9217-0E06-41DA-8B02-64C8D2DD3F41}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286A5F74-DB3F-456B-BB92-62E379DF2CD9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="870" firstSheet="4" activeTab="16" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="870" firstSheet="5" activeTab="17" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseyear" sheetId="12" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="CTAX_CPS" sheetId="24" r:id="rId15"/>
     <sheet name="CTAX_NZS" sheetId="25" r:id="rId16"/>
     <sheet name="PERMIT" sheetId="29" r:id="rId17"/>
+    <sheet name="TIW_Share_Cal" sheetId="30" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">GDP_Projection!$A$1:$CF$18</definedName>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="115">
   <si>
     <t>01_KOR</t>
   </si>
@@ -332,6 +333,99 @@
   <si>
     <t>BAU</t>
   </si>
+  <si>
+    <t>01_AGRICULT</t>
+  </si>
+  <si>
+    <t>02_COAL</t>
+  </si>
+  <si>
+    <t>03_OIL</t>
+  </si>
+  <si>
+    <t>04_GAS</t>
+  </si>
+  <si>
+    <t>05_MINING</t>
+  </si>
+  <si>
+    <t>06_FOODPRO</t>
+  </si>
+  <si>
+    <t>07_TEXTILES</t>
+  </si>
+  <si>
+    <t>08_WOODPRO</t>
+  </si>
+  <si>
+    <t>09_PAPERPRO</t>
+  </si>
+  <si>
+    <t>10_PETROLCOAL</t>
+  </si>
+  <si>
+    <t>11_CHEMICAL</t>
+  </si>
+  <si>
+    <t>12_NONMET</t>
+  </si>
+  <si>
+    <t>13_IRONSTL</t>
+  </si>
+  <si>
+    <t>14_NONFERR</t>
+  </si>
+  <si>
+    <t>15_MACHINE</t>
+  </si>
+  <si>
+    <t>16_TRANSEQ</t>
+  </si>
+  <si>
+    <t>17_OTHERIND</t>
+  </si>
+  <si>
+    <t>20_eCoal</t>
+  </si>
+  <si>
+    <t>21_eGas</t>
+  </si>
+  <si>
+    <t>22_eOil</t>
+  </si>
+  <si>
+    <t>27_CONSTRUC</t>
+  </si>
+  <si>
+    <t>28_LTRP</t>
+  </si>
+  <si>
+    <t>29_WTRP</t>
+  </si>
+  <si>
+    <t>30_ATRP</t>
+  </si>
+  <si>
+    <t>31_SER</t>
+  </si>
+  <si>
+    <t>18_TnD</t>
+  </si>
+  <si>
+    <t>19_eNuclear</t>
+  </si>
+  <si>
+    <t>23_eWind</t>
+  </si>
+  <si>
+    <t>24_eSolar</t>
+  </si>
+  <si>
+    <t>25_eHydro</t>
+  </si>
+  <si>
+    <t>26_eOther</t>
+  </si>
 </sst>
 </file>
 
@@ -552,6 +646,1067 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PERMIT!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>01_KOR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>PERMIT!$B$1:$AG$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PERMIT!$B$2:$AG$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94604383440336504</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.93836764814404838</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.91335547192089139</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.90154084569404469</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.89067522692052248</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.84222935576710201</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.79378348461368153</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.74533761346026117</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.69689174230684081</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.64844587115342034</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.57499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.52500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.47499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.42500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.35000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.32500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.30000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.27500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.25000000000000006</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.22500000000000003</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.17500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.15000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.12500000000000006</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.10000000000000009</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-74E6-4C85-B43F-4F5A62937E39}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="418189439"/>
+        <c:axId val="492946847"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="418189439"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="492946847"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="492946847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="418189439"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>576943</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>157843</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>326571</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>32657</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFE164EC-474B-4C50-B9A5-082E3709680E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16529,71 +17684,71 @@
         <v>0.64844587115342034</v>
       </c>
       <c r="M2" s="41">
-        <v>0.59999999999999987</v>
+        <v>0.6</v>
       </c>
       <c r="N2" s="41">
-        <v>0.5704999999999999</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="O2" s="41">
-        <v>0.54099999999999993</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="P2" s="41">
-        <v>0.51149999999999984</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="Q2" s="41">
-        <v>0.48199999999999987</v>
+        <v>0.5</v>
       </c>
       <c r="R2" s="41">
-        <v>0.4524999999999999</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="S2" s="41">
-        <v>0.42299999999999993</v>
+        <v>0.45</v>
       </c>
       <c r="T2" s="41">
-        <v>0.39349999999999996</v>
+        <v>0.42500000000000004</v>
       </c>
       <c r="U2" s="41">
-        <v>0.36399999999999993</v>
+        <v>0.4</v>
       </c>
       <c r="V2" s="41">
-        <v>0.33449999999999996</v>
+        <v>0.375</v>
       </c>
       <c r="W2" s="41">
-        <v>0.30499999999999999</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="X2" s="41">
-        <v>0.27549999999999997</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="Y2" s="41">
-        <v>0.246</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="Z2" s="41">
-        <v>0.21650000000000003</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="AA2" s="41">
-        <v>0.187</v>
+        <v>0.25000000000000006</v>
       </c>
       <c r="AB2" s="41">
-        <v>0.15750000000000003</v>
+        <v>0.22500000000000003</v>
       </c>
       <c r="AC2" s="41">
-        <v>0.128</v>
+        <v>0.2</v>
       </c>
       <c r="AD2" s="41">
-        <v>9.8500000000000032E-2</v>
+        <v>0.17500000000000004</v>
       </c>
       <c r="AE2" s="41">
-        <v>6.9000000000000061E-2</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="AF2" s="41">
-        <v>3.9500000000000091E-2</v>
+        <v>0.12500000000000006</v>
       </c>
       <c r="AG2" s="41">
-        <v>1.000000000000012E-2</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AI2" s="27">
         <f>(AG2-E2)/$AI$1</f>
-        <v>-3.226269542574612E-2</v>
+        <v>-2.9048409711460405E-2</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
@@ -22619,6 +23774,4372 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D08F80-207D-43E9-8A3A-6CB519395E3B}">
+  <dimension ref="A1:AG33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2026</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2027</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2028</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2029</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2030</v>
+      </c>
+      <c r="N1" s="1">
+        <v>2031</v>
+      </c>
+      <c r="O1" s="1">
+        <v>2032</v>
+      </c>
+      <c r="P1" s="1">
+        <v>2033</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>2034</v>
+      </c>
+      <c r="R1" s="1">
+        <v>2035</v>
+      </c>
+      <c r="S1" s="1">
+        <v>2036</v>
+      </c>
+      <c r="T1" s="1">
+        <v>2037</v>
+      </c>
+      <c r="U1" s="1">
+        <v>2038</v>
+      </c>
+      <c r="V1" s="1">
+        <v>2039</v>
+      </c>
+      <c r="W1" s="1">
+        <v>2040</v>
+      </c>
+      <c r="X1" s="1">
+        <v>2041</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>2042</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>2043</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>2044</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>2045</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>2046</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>2047</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>2048</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>2049</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="27">
+        <f>1/31</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C2" s="27">
+        <f>B2</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D2" s="27">
+        <f t="shared" ref="D2:AG10" si="0">C2</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG2" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="27">
+        <f>1/31</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C3" s="27">
+        <f t="shared" ref="C3:R32" si="1">B3</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R3" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG3" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="27">
+        <f>1/31</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C4" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG4" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="27">
+        <f>1/31</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C5" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="27">
+        <f>1/31</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C6" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG6" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="27">
+        <f t="shared" ref="B7:B32" si="2">1/31</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C7" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG7" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C8" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG8" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C9" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG9" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C10" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG10" s="27">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C11" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D11" s="27">
+        <f t="shared" ref="D11:AG19" si="3">C11</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C12" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C13" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG13" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C14" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG14" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C15" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG15" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C16" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG16" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C17" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG17" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C18" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG18" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C19" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R19" s="27">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S19" s="27">
+        <f t="shared" ref="D19:AG27" si="4">R19</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG19" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C20" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG20" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="27">
+        <f>1-SUM(B2:B20)-SUM(B22:B32)</f>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="C21" s="27">
+        <f t="shared" si="1"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="D21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="E21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="F21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="G21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="H21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="I21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="J21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="K21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="L21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="M21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="N21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="O21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="P21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="Q21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="R21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="S21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="T21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="U21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="V21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="W21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="X21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="Y21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="Z21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="AA21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="AB21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="AC21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="AD21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="AE21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="AF21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+      <c r="AG21" s="27">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258451E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C22" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG22" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="27">
+        <v>0</v>
+      </c>
+      <c r="C23" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AE23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C24" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG24" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C25" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG25" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C26" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG26" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C27" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG27" s="27">
+        <f t="shared" si="4"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C28" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D28" s="27">
+        <f t="shared" ref="D28:AG32" si="5">C28</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG28" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C29" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG29" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C30" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG30" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C31" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG31" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="27">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="C32" s="27">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="D32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="E32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="G32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="H32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="I32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="J32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="L32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="M32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="O32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="P32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Q32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="R32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="S32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="T32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="U32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="W32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Y32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="Z32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AA32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AB32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AC32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AD32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AE32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AF32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="AG32" s="27">
+        <f t="shared" si="5"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <f>SUM(B2:B32)</f>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="C33">
+        <f t="shared" ref="C33:AG33" si="6">SUM(C2:C32)</f>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="P33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="T33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="U33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="V33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="W33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="X33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="Y33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="Z33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="AA33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="AB33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="AC33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="AD33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="AE33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="AF33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="AG33">
+        <f t="shared" si="6"/>
+        <v>0.99999999999999978</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
